--- a/internacional/Contraste_tierra_espacio.xlsx
+++ b/internacional/Contraste_tierra_espacio.xlsx
@@ -611,11 +611,14 @@
       <c r="I2" t="n">
         <v>10</v>
       </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
       <c r="K2" t="n">
         <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -762,13 +765,13 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
         <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -834,7 +837,7 @@
         <v>9.5</v>
       </c>
       <c r="M7" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
@@ -933,10 +936,10 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -987,7 +990,7 @@
         <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
@@ -1020,7 +1023,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -1065,10 +1074,13 @@
         <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1121,6 +1133,9 @@
       <c r="J13" t="n">
         <v>9</v>
       </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
       <c r="M13" t="n">
         <v>9.5</v>
       </c>
@@ -1166,6 +1181,15 @@
       <c r="I14" t="n">
         <v>3</v>
       </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
@@ -1247,6 +1271,9 @@
       <c r="J16" t="n">
         <v>9</v>
       </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
       <c r="M16" t="n">
         <v>9.5</v>
       </c>
@@ -1298,8 +1325,14 @@
       <c r="G17" t="n">
         <v>6</v>
       </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
       <c r="M17" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -1350,10 +1383,10 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M18" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1406,8 +1439,11 @@
       <c r="I19" t="n">
         <v>8</v>
       </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
       <c r="M19" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="V19" t="n">
         <v>1</v>
@@ -1439,6 +1475,12 @@
       <c r="G20" t="n">
         <v>3</v>
       </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7</v>
+      </c>
       <c r="Y20" t="n">
         <v>1</v>
       </c>
@@ -1472,6 +1514,9 @@
       <c r="I21" t="n">
         <v>9.5</v>
       </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
@@ -1511,6 +1556,9 @@
       <c r="I22" t="n">
         <v>4</v>
       </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
       <c r="K22" t="n">
         <v>9</v>
       </c>
@@ -1553,6 +1601,9 @@
       <c r="G23" t="n">
         <v>8.5</v>
       </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
@@ -1593,7 +1644,7 @@
         <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -1646,8 +1697,14 @@
       <c r="I25" t="n">
         <v>2</v>
       </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
       <c r="M25" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -1685,6 +1742,12 @@
       <c r="G26" t="n">
         <v>8.5</v>
       </c>
+      <c r="J26" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" t="n">
+        <v>8</v>
+      </c>
       <c r="M26" t="n">
         <v>9.5</v>
       </c>
@@ -1733,11 +1796,14 @@
       <c r="I27" t="n">
         <v>7</v>
       </c>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
       <c r="K27" t="n">
         <v>9</v>
       </c>
       <c r="M27" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -1787,8 +1853,11 @@
       <c r="I28" t="n">
         <v>8</v>
       </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
       <c r="M28" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="V28" t="n">
         <v>1</v>
@@ -1875,10 +1944,13 @@
         <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -1938,7 +2010,10 @@
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8</v>
       </c>
       <c r="M32" t="n">
         <v>9.5</v>
@@ -2013,7 +2088,7 @@
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
         <v>9</v>
@@ -2022,7 +2097,7 @@
         <v>9.5</v>
       </c>
       <c r="M33" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
@@ -2087,6 +2162,9 @@
       <c r="L34" t="n">
         <v>9.5</v>
       </c>
+      <c r="M34" t="n">
+        <v>7</v>
+      </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
@@ -2145,13 +2223,13 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L35" t="n">
         <v>9.5</v>
       </c>
       <c r="M35" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -2226,16 +2304,16 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L36" t="n">
         <v>9.5</v>
       </c>
       <c r="M36" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
@@ -2306,6 +2384,9 @@
       <c r="G37" t="n">
         <v>6</v>
       </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
@@ -2361,7 +2442,7 @@
         <v>9</v>
       </c>
       <c r="K38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M38" t="n">
         <v>9.5</v>
@@ -2420,14 +2501,17 @@
       <c r="I39" t="n">
         <v>9.5</v>
       </c>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
       <c r="K39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L39" t="n">
         <v>9.5</v>
       </c>
       <c r="M39" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -2505,7 +2589,7 @@
         <v>9.5</v>
       </c>
       <c r="M40" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -2580,7 +2664,7 @@
         <v>9.5</v>
       </c>
       <c r="M41" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
@@ -2645,11 +2729,14 @@
       <c r="I42" t="n">
         <v>8</v>
       </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
       <c r="K42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M42" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -2702,6 +2789,9 @@
       <c r="G43" t="n">
         <v>8.5</v>
       </c>
+      <c r="M43" t="n">
+        <v>7</v>
+      </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
@@ -2768,6 +2858,9 @@
       <c r="E45" t="n">
         <v>7</v>
       </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
       <c r="M45" t="n">
         <v>9.5</v>
       </c>
@@ -2810,6 +2903,15 @@
       <c r="E46" t="n">
         <v>6</v>
       </c>
+      <c r="J46" t="n">
+        <v>7</v>
+      </c>
+      <c r="K46" t="n">
+        <v>8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>7</v>
+      </c>
       <c r="AB46" t="n">
         <v>1</v>
       </c>
@@ -2841,7 +2943,7 @@
         <v>4</v>
       </c>
       <c r="M47" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
@@ -2891,6 +2993,12 @@
       <c r="D48" t="n">
         <v>9</v>
       </c>
+      <c r="J48" t="n">
+        <v>7</v>
+      </c>
+      <c r="K48" t="n">
+        <v>8</v>
+      </c>
       <c r="M48" t="n">
         <v>9.5</v>
       </c>
@@ -2946,7 +3054,7 @@
         <v>9</v>
       </c>
       <c r="M49" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -3011,8 +3119,11 @@
       <c r="J50" t="n">
         <v>9</v>
       </c>
+      <c r="K50" t="n">
+        <v>8</v>
+      </c>
       <c r="M50" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
@@ -3074,8 +3185,14 @@
       <c r="I51" t="n">
         <v>9.5</v>
       </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>8</v>
+      </c>
       <c r="M51" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
@@ -3125,6 +3242,9 @@
       <c r="I52" t="n">
         <v>10</v>
       </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
       <c r="K52" t="n">
         <v>9</v>
       </c>
@@ -3180,13 +3300,13 @@
         <v>7</v>
       </c>
       <c r="J53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K53" t="n">
         <v>9</v>
       </c>
       <c r="M53" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -3242,8 +3362,11 @@
       <c r="I54" t="n">
         <v>10</v>
       </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
       <c r="M54" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
@@ -3291,7 +3414,7 @@
         <v>9.5</v>
       </c>
       <c r="M55" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -3335,6 +3458,9 @@
       <c r="G56" t="n">
         <v>6</v>
       </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
@@ -3372,7 +3498,7 @@
         <v>10.5</v>
       </c>
       <c r="M57" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
@@ -3467,8 +3593,11 @@
       <c r="I59" t="n">
         <v>6</v>
       </c>
+      <c r="J59" t="n">
+        <v>7</v>
+      </c>
       <c r="M59" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O59" t="n">
         <v>1</v>
@@ -3527,6 +3656,9 @@
       <c r="K60" t="n">
         <v>9</v>
       </c>
+      <c r="M60" t="n">
+        <v>7</v>
+      </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
@@ -3560,8 +3692,14 @@
       <c r="I61" t="n">
         <v>8</v>
       </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
       <c r="M61" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O61" t="n">
         <v>1</v>
@@ -3612,7 +3750,7 @@
         <v>8.5</v>
       </c>
       <c r="M62" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
@@ -3695,8 +3833,11 @@
       <c r="I64" t="n">
         <v>10</v>
       </c>
+      <c r="J64" t="n">
+        <v>7</v>
+      </c>
       <c r="M64" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -3747,13 +3888,13 @@
         <v>7</v>
       </c>
       <c r="J65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M65" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
@@ -3821,8 +3962,11 @@
       <c r="I66" t="n">
         <v>9.5</v>
       </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
       <c r="M66" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O66" t="n">
         <v>1</v>
@@ -3873,10 +4017,10 @@
         <v>6</v>
       </c>
       <c r="J67" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M67" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -3950,8 +4094,11 @@
       <c r="I69" t="n">
         <v>5</v>
       </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
       <c r="M69" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
@@ -4008,10 +4155,13 @@
         <v>8</v>
       </c>
       <c r="J70" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K70" t="n">
+        <v>8</v>
       </c>
       <c r="M70" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
@@ -4068,13 +4218,13 @@
         <v>9.5</v>
       </c>
       <c r="J71" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K71" t="n">
         <v>9</v>
       </c>
       <c r="M71" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
@@ -4145,6 +4295,9 @@
       <c r="I72" t="n">
         <v>3</v>
       </c>
+      <c r="J72" t="n">
+        <v>7</v>
+      </c>
       <c r="O72" t="n">
         <v>1</v>
       </c>
@@ -4188,10 +4341,10 @@
         <v>6</v>
       </c>
       <c r="J73" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M73" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -4253,8 +4406,11 @@
       <c r="I74" t="n">
         <v>3</v>
       </c>
+      <c r="J74" t="n">
+        <v>7</v>
+      </c>
       <c r="M74" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -4302,7 +4458,7 @@
         <v>6</v>
       </c>
       <c r="M75" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -4361,6 +4517,12 @@
       <c r="I76" t="n">
         <v>6</v>
       </c>
+      <c r="J76" t="n">
+        <v>7</v>
+      </c>
+      <c r="M76" t="n">
+        <v>7</v>
+      </c>
       <c r="O76" t="n">
         <v>1</v>
       </c>
@@ -4444,6 +4606,9 @@
       </c>
       <c r="I78" t="n">
         <v>5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>

--- a/internacional/Contraste_tierra_espacio.xlsx
+++ b/internacional/Contraste_tierra_espacio.xlsx
@@ -2151,7 +2151,7 @@
         <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G34" t="n">
         <v>8.5</v>
@@ -2159,24 +2159,15 @@
       <c r="K34" t="n">
         <v>9</v>
       </c>
-      <c r="L34" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M34" t="n">
         <v>7</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
@@ -2184,15 +2175,6 @@
         <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE34" t="n">
         <v>1</v>
       </c>
     </row>

--- a/internacional/Contraste_tierra_espacio.xlsx
+++ b/internacional/Contraste_tierra_espacio.xlsx
@@ -747,145 +747,97 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Capas de la atmósfera y variación con la altitud</t>
+          <t>Aguas subterráneas y acuíferos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>9</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Capas internas de la Tierra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
         <v>7</v>
       </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
       <c r="Y7" t="n">
         <v>1</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
         <v>1</v>
       </c>
       <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aguas subterráneas y acuíferos</t>
+          <t>Ciclones tropicales y tormentas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,28 +846,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capas internas de la Tierra</t>
+          <t>El Sol como estrella</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -924,38 +876,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>7</v>
       </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
       <c r="Y9" t="n">
         <v>1</v>
       </c>
@@ -966,16 +909,13 @@
         <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ciclones tropicales y tormentas</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -986,26 +926,59 @@
       <c r="C10" t="n">
         <v>4</v>
       </c>
+      <c r="F10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
       </c>
       <c r="M10" t="n">
         <v>7</v>
       </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1</v>
       </c>
       <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Sol como estrella</t>
+          <t>Ciclo de vida de las estrellas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1014,30 +987,30 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10.5</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
         <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
         <v>1</v>
       </c>
       <c r="AA11" t="n">
@@ -1047,13 +1020,16 @@
         <v>1</v>
       </c>
       <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1064,12 +1040,6 @@
       <c r="C12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
@@ -1082,33 +1052,6 @@
       <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1</v>
-      </c>
       <c r="AE12" t="n">
         <v>1</v>
       </c>
@@ -1116,7 +1059,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las estrellas</t>
+          <t>Formación y evolución temprana de la Tierra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1125,21 +1068,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10.5</v>
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
       </c>
       <c r="J13" t="n">
         <v>9</v>
       </c>
-      <c r="K13" t="n">
-        <v>8</v>
-      </c>
       <c r="M13" t="n">
         <v>9.5</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
@@ -1148,10 +1094,10 @@
       <c r="V13" t="n">
         <v>1</v>
       </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1</v>
       </c>
       <c r="AB13" t="n">
@@ -1167,7 +1113,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Formación del sistema solar</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1178,26 +1124,50 @@
       <c r="C14" t="n">
         <v>4</v>
       </c>
+      <c r="F14" t="n">
+        <v>10.5</v>
+      </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
         <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Formación y evolución temprana de la Tierra</t>
+          <t>Galaxias y escala del universo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1206,36 +1176,42 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10.5</v>
       </c>
       <c r="G15" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1</v>
       </c>
       <c r="AB15" t="n">
@@ -1251,7 +1227,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Formación del sistema solar</t>
+          <t>Impacto de las actividades humanas en los recursos</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1260,35 +1236,32 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
         <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="V16" t="n">
         <v>1</v>
       </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
@@ -1299,13 +1272,16 @@
         <v>1</v>
       </c>
       <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Galaxias y escala del universo</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1314,19 +1290,16 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
         <v>5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10.5</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
       </c>
-      <c r="J17" t="n">
-        <v>7</v>
+      <c r="I17" t="n">
+        <v>8</v>
       </c>
       <c r="K17" t="n">
         <v>8</v>
@@ -1334,25 +1307,10 @@
       <c r="M17" t="n">
         <v>7</v>
       </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
       <c r="V17" t="n">
         <v>1</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="n">
         <v>1</v>
       </c>
       <c r="AC17" t="n">
@@ -1365,7 +1323,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Impacto de las actividades humanas en los recursos</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1374,35 +1332,17 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8</v>
-      </c>
-      <c r="I18" t="n">
-        <v>8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
       </c>
       <c r="M18" t="n">
         <v>7</v>
       </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
       <c r="Y18" t="n">
         <v>1</v>
       </c>
@@ -1410,16 +1350,13 @@
         <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1428,40 +1365,43 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
         <v>4</v>
       </c>
-      <c r="E19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>6</v>
+      <c r="F19" t="n">
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8</v>
-      </c>
-      <c r="M19" t="n">
-        <v>7</v>
-      </c>
-      <c r="V19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1</v>
       </c>
       <c r="AA19" t="n">
         <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1472,29 +1412,41 @@
       <c r="C20" t="n">
         <v>4</v>
       </c>
-      <c r="G20" t="n">
-        <v>3</v>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
       </c>
       <c r="J20" t="n">
         <v>7</v>
       </c>
+      <c r="K20" t="n">
+        <v>9</v>
+      </c>
       <c r="M20" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
         <v>1</v>
       </c>
       <c r="AB20" t="n">
         <v>1</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1503,16 +1455,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
-      <c r="I21" t="n">
-        <v>9.5</v>
+      <c r="G21" t="n">
+        <v>8.5</v>
       </c>
       <c r="J21" t="n">
         <v>7</v>
@@ -1520,26 +1469,26 @@
       <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
       <c r="Y21" t="n">
         <v>1</v>
       </c>
-      <c r="AA21" t="n">
-        <v>1</v>
-      </c>
       <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Registro fósil y cambios ambientales del pasado</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1548,24 +1497,18 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
         <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O22" t="n">
+        <v>7</v>
+      </c>
+      <c r="R22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
@@ -1574,7 +1517,19 @@
       <c r="V22" t="n">
         <v>1</v>
       </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
       <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
@@ -1584,7 +1539,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1593,30 +1548,36 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="n">
         <v>8</v>
       </c>
-      <c r="F23" t="n">
-        <v>8</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="M23" t="n">
+        <v>7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
         <v>1</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="n">
@@ -1626,7 +1587,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Registro fósil y cambios ambientales del pasado</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1635,21 +1596,24 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O24" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="n">
@@ -1658,6 +1622,9 @@
       <c r="W24" t="n">
         <v>1</v>
       </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
       <c r="Y24" t="n">
         <v>1</v>
       </c>
@@ -1668,16 +1635,13 @@
         <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1686,27 +1650,27 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M25" t="n">
         <v>7</v>
       </c>
-      <c r="R25" t="n">
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="n">
@@ -1715,7 +1679,13 @@
       <c r="W25" t="n">
         <v>1</v>
       </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
       <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1</v>
       </c>
       <c r="AE25" t="n">
@@ -1725,7 +1695,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1734,25 +1704,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
-      </c>
-      <c r="F26" t="n">
-        <v>10.5</v>
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>8.5</v>
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
       </c>
-      <c r="K26" t="n">
-        <v>8</v>
-      </c>
       <c r="M26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V26" t="n">
         <v>1</v>
@@ -1760,26 +1727,17 @@
       <c r="W26" t="n">
         <v>1</v>
       </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1</v>
-      </c>
       <c r="AA26" t="n">
         <v>1</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Tsunamis</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1790,116 +1748,107 @@
       <c r="C27" t="n">
         <v>4</v>
       </c>
-      <c r="F27" t="n">
-        <v>8</v>
-      </c>
-      <c r="I27" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K27" t="n">
-        <v>9</v>
-      </c>
-      <c r="M27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="Y27" t="n">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Acidificación del océano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" t="n">
-        <v>8</v>
-      </c>
-      <c r="J28" t="n">
-        <v>7</v>
-      </c>
-      <c r="M28" t="n">
-        <v>7</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tsunamis</t>
+          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" t="n">
         <v>4</v>
       </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
         <v>1</v>
       </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
       <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Acidificación del océano</t>
+          <t>Origen del universo: el Big Bang</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1908,22 +1857,73 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" t="n">
         <v>9</v>
       </c>
       <c r="F30" t="n">
         <v>10.5</v>
       </c>
+      <c r="I30" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
       <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1932,51 +1932,63 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" t="n">
         <v>9</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
         <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9.5</v>
       </c>
       <c r="M31" t="n">
         <v>7</v>
       </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="X31" t="n">
         <v>1</v>
       </c>
       <c r="AE31" t="n">
@@ -1986,7 +1998,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Origen del universo: el Big Bang</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1995,42 +2007,27 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
-      </c>
-      <c r="E32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F32" t="n">
         <v>10.5</v>
       </c>
-      <c r="I32" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" t="n">
-        <v>7</v>
+      <c r="G32" t="n">
+        <v>8.5</v>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="n">
+      <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="W32" t="n">
@@ -2040,28 +2037,13 @@
         <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2070,12 +2052,9 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
-      </c>
-      <c r="E33" t="n">
         <v>9</v>
       </c>
       <c r="F33" t="n">
@@ -2090,18 +2069,12 @@
       <c r="J33" t="n">
         <v>7</v>
       </c>
-      <c r="K33" t="n">
-        <v>9</v>
-      </c>
       <c r="L33" t="n">
         <v>9.5</v>
       </c>
       <c r="M33" t="n">
         <v>7</v>
       </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
       <c r="O33" t="n">
         <v>1</v>
       </c>
@@ -2114,9 +2087,6 @@
       <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
       <c r="U33" t="n">
         <v>1</v>
       </c>
@@ -2126,7 +2096,22 @@
       <c r="W33" t="n">
         <v>1</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1</v>
       </c>
       <c r="AE33" t="n">
@@ -2136,7 +2121,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Capas de la atmósfera y variación con la altitud</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2145,16 +2130,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
         <v>10.5</v>
       </c>
-      <c r="G34" t="n">
-        <v>8.5</v>
+      <c r="I34" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
       </c>
       <c r="K34" t="n">
         <v>9</v>
@@ -2165,23 +2150,35 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2190,9 +2187,12 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
         <v>9</v>
       </c>
       <c r="F35" t="n">
@@ -2207,12 +2207,18 @@
       <c r="J35" t="n">
         <v>7</v>
       </c>
+      <c r="K35" t="n">
+        <v>8</v>
+      </c>
       <c r="L35" t="n">
         <v>9.5</v>
       </c>
       <c r="M35" t="n">
         <v>7</v>
       </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
@@ -2225,6 +2231,9 @@
       <c r="S35" t="n">
         <v>1</v>
       </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
@@ -2234,22 +2243,16 @@
       <c r="W35" t="n">
         <v>1</v>
       </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
       <c r="Y35" t="n">
         <v>1</v>
       </c>
-      <c r="Z35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1</v>
-      </c>
       <c r="AB35" t="n">
         <v>1</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD35" t="n">
         <v>1</v>
       </c>
       <c r="AE35" t="n">
@@ -2259,7 +2262,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Ciclo de las rocas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2268,66 +2271,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G36" t="n">
         <v>6</v>
       </c>
-      <c r="I36" t="n">
-        <v>10</v>
-      </c>
       <c r="J36" t="n">
         <v>7</v>
       </c>
-      <c r="K36" t="n">
-        <v>8</v>
-      </c>
-      <c r="L36" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>7</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
-      <c r="X36" t="n">
-        <v>1</v>
-      </c>
       <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>1</v>
       </c>
       <c r="AB36" t="n">
@@ -2343,7 +2313,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ciclo de las rocas</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2352,39 +2322,51 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="n">
         <v>3</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
         <v>9</v>
       </c>
-      <c r="E37" t="n">
-        <v>7</v>
-      </c>
-      <c r="F37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" t="n">
-        <v>7</v>
+      <c r="K37" t="n">
+        <v>8</v>
+      </c>
+      <c r="M37" t="n">
+        <v>9.5</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="Y37" t="n">
         <v>1</v>
       </c>
-      <c r="AA37" t="n">
-        <v>1</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC37" t="n">
         <v>1</v>
       </c>
       <c r="AE37" t="n">
@@ -2394,7 +2376,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2403,51 +2385,75 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
         <v>8</v>
       </c>
+      <c r="L38" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M38" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
         <v>1</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
       <c r="Y38" t="n">
         <v>1</v>
       </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
       <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1</v>
       </c>
       <c r="AE38" t="n">
@@ -2457,7 +2463,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2466,13 +2472,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
-      </c>
-      <c r="E39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -2480,14 +2483,8 @@
       <c r="G39" t="n">
         <v>6</v>
       </c>
-      <c r="I39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>7</v>
-      </c>
       <c r="K39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L39" t="n">
         <v>9.5</v>
@@ -2501,9 +2498,6 @@
       <c r="P39" t="n">
         <v>1</v>
       </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
@@ -2523,9 +2517,6 @@
         <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA39" t="n">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
@@ -2544,7 +2535,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2553,17 +2544,20 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G40" t="n">
         <v>6</v>
       </c>
+      <c r="I40" t="n">
+        <v>10</v>
+      </c>
       <c r="K40" t="n">
         <v>9</v>
       </c>
@@ -2579,6 +2573,9 @@
       <c r="P40" t="n">
         <v>1</v>
       </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
@@ -2591,22 +2588,16 @@
       <c r="W40" t="n">
         <v>1</v>
       </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
       <c r="Y40" t="n">
         <v>1</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AA40" t="n">
         <v>1</v>
       </c>
       <c r="AB40" t="n">
         <v>1</v>
       </c>
       <c r="AC40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD40" t="n">
         <v>1</v>
       </c>
       <c r="AE40" t="n">
@@ -2616,7 +2607,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2625,25 +2616,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F41" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>9</v>
-      </c>
-      <c r="L41" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="M41" t="n">
         <v>7</v>
@@ -2651,28 +2642,19 @@
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
       <c r="V41" t="n">
         <v>1</v>
       </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
       <c r="Y41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="n">
         <v>1</v>
       </c>
       <c r="AB41" t="n">
@@ -2688,7 +2670,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2697,7 +2679,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
         <v>11</v>
@@ -2706,16 +2688,7 @@
         <v>8</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8</v>
-      </c>
-      <c r="J42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K42" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M42" t="n">
         <v>7</v>
@@ -2723,12 +2696,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1</v>
-      </c>
       <c r="W42" t="n">
         <v>1</v>
       </c>
@@ -2736,12 +2703,6 @@
         <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC42" t="n">
         <v>1</v>
       </c>
       <c r="AE42" t="n">
@@ -2751,7 +2712,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2763,37 +2724,25 @@
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
       </c>
-      <c r="G43" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M43" t="n">
-        <v>7</v>
+      <c r="I43" t="n">
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="W43" t="n">
-        <v>1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1</v>
-      </c>
       <c r="Y43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE43" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Deriva continental y expansión del fondo oceánico</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2802,28 +2751,43 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="F44" t="n">
-        <v>8</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3</v>
-      </c>
-      <c r="O44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
+      <c r="M44" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="Y44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico</t>
+          <t>Eclipses solares y lunares</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2832,43 +2796,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
         <v>7</v>
       </c>
+      <c r="K45" t="n">
+        <v>8</v>
+      </c>
       <c r="M45" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Eclipses solares y lunares</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2877,24 +2829,72 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
-      </c>
-      <c r="D46" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="L46" t="n">
+        <v>9.5</v>
       </c>
       <c r="M46" t="n">
         <v>7</v>
       </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
       <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
         <v>1</v>
       </c>
     </row>

--- a/internacional/Contraste_tierra_espacio.xlsx
+++ b/internacional/Contraste_tierra_espacio.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE80"/>
+  <dimension ref="A1:AH80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -587,6 +587,21 @@
           <t>TW esp</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Grado SV solido</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura amplia</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura estricta</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -644,90 +659,195 @@
       <c r="AE2" t="n">
         <v>1</v>
       </c>
+      <c r="AF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Convección del manto y energía interna de la Tierra</t>
+          <t>Acidificación del océano</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no_aplica</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" t="n">
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
         <v>9</v>
       </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1</v>
+      <c r="F3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Energía geotérmica</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no_aplica</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>no_retomado</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no_aplica</t>
-        </is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>10.5</v>
       </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
       <c r="K5" t="n">
         <v>9</v>
       </c>
+      <c r="L5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M5" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
@@ -737,68 +857,106 @@
       <c r="Y5" t="n">
         <v>1</v>
       </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
       <c r="AB5" t="n">
         <v>1</v>
       </c>
       <c r="AC5" t="n">
         <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>no_retomado</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aguas subterráneas y acuíferos</t>
+          <t>Convección del manto y energía interna de la Tierra</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
       <c r="AC6" t="n">
         <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>solo_especializacion</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>no_aplica</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Capas internas de la Tierra</t>
+          <t>Oleaje, dinámica costera y sedimentación marina</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="M7" t="n">
         <v>7</v>
@@ -806,18 +964,9 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="W7" t="n">
-        <v>1</v>
-      </c>
       <c r="Y7" t="n">
         <v>1</v>
       </c>
@@ -827,158 +976,150 @@
       <c r="AB7" t="n">
         <v>1</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
+      <c r="AF7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ciclones tropicales y tormentas</t>
+          <t>Energía geotérmica</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>no_aplica</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>El Sol como estrella</t>
+          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10.5</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>1</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1</v>
-      </c>
       <c r="AB9" t="n">
         <v>1</v>
       </c>
       <c r="AC9" t="n">
         <v>1</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>no_aplica</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Tsunamis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K10" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>1</v>
       </c>
-      <c r="AA10" t="n">
-        <v>1</v>
-      </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
-      <c r="AC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1</v>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>no_aplica</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las estrellas</t>
+          <t>Aguas subterráneas y acuíferos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -987,49 +1128,44 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>9</v>
-      </c>
-      <c r="K11" t="n">
         <v>8</v>
       </c>
-      <c r="M11" t="n">
-        <v>9.5</v>
+      <c r="I11" t="n">
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="n">
         <v>1</v>
       </c>
       <c r="AC11" t="n">
         <v>1</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1</v>
+      <c r="AF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Capas internas de la Tierra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1038,28 +1174,71 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
       </c>
       <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Formación y evolución temprana de la Tierra</t>
+          <t>Ciclo de las rocas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1068,30 +1247,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.5</v>
       </c>
       <c r="G13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
-      </c>
-      <c r="M13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
         <v>1</v>
       </c>
       <c r="W13" t="n">
@@ -1100,6 +1273,9 @@
       <c r="Y13" t="n">
         <v>1</v>
       </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
       <c r="AB13" t="n">
         <v>1</v>
       </c>
@@ -1108,12 +1284,25 @@
       </c>
       <c r="AE13" t="n">
         <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Formación del sistema solar</t>
+          <t>Ciclones tropicales y tormentas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1124,50 +1313,42 @@
       <c r="C14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" t="n">
-        <v>10.5</v>
+      <c r="D14" t="n">
+        <v>11</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V14" t="n">
         <v>1</v>
       </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
         <v>1</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1</v>
+      <c r="AF14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Galaxias y escala del universo</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1176,33 +1357,24 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M15" t="n">
         <v>7</v>
       </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
@@ -1211,23 +1383,27 @@
       <c r="Y15" t="n">
         <v>1</v>
       </c>
-      <c r="AA15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1</v>
-      </c>
       <c r="AE15" t="n">
         <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Impacto de las actividades humanas en los recursos</t>
+          <t>Eclipses solares y lunares</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,13 +1412,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7</v>
       </c>
       <c r="K16" t="n">
         <v>8</v>
@@ -1250,38 +1429,27 @@
       <c r="M16" t="n">
         <v>7</v>
       </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1</v>
-      </c>
       <c r="AB16" t="n">
         <v>1</v>
       </c>
-      <c r="AC16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1</v>
+      <c r="AF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>El Sol como estrella</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1290,10 +1458,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
@@ -1301,29 +1469,51 @@
       <c r="I17" t="n">
         <v>8</v>
       </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
       <c r="K17" t="n">
         <v>8</v>
       </c>
       <c r="M17" t="n">
         <v>7</v>
       </c>
-      <c r="V17" t="n">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
         <v>1</v>
       </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
       <c r="AC17" t="n">
         <v>1</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1</v>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1334,29 +1524,72 @@
       <c r="C18" t="n">
         <v>4</v>
       </c>
+      <c r="F18" t="n">
+        <v>10.5</v>
+      </c>
       <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="n">
         <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>7</v>
       </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
       <c r="M18" t="n">
         <v>7</v>
       </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
       <c r="Y18" t="n">
         <v>1</v>
       </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
       <c r="AB18" t="n">
         <v>1</v>
       </c>
       <c r="AC18" t="n">
         <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Ciclo de vida de las estrellas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1367,41 +1600,60 @@
       <c r="C19" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
       <c r="F19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>9</v>
+      </c>
+      <c r="K19" t="n">
         <v>8</v>
       </c>
-      <c r="I19" t="n">
+      <c r="M19" t="n">
         <v>9.5</v>
       </c>
-      <c r="J19" t="n">
-        <v>7</v>
-      </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
         <v>1</v>
       </c>
       <c r="AA19" t="n">
         <v>1</v>
       </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
       <c r="AC19" t="n">
         <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1412,41 +1664,42 @@
       <c r="C20" t="n">
         <v>4</v>
       </c>
-      <c r="F20" t="n">
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" t="n">
         <v>8</v>
       </c>
-      <c r="I20" t="n">
+      <c r="M20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
         <v>4</v>
       </c>
-      <c r="J20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>9</v>
-      </c>
-      <c r="M20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1</v>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Formación y evolución temprana de la Tierra</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1455,40 +1708,65 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
-      </c>
-      <c r="F21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>8.5</v>
       </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
       <c r="J21" t="n">
-        <v>7</v>
-      </c>
-      <c r="O21" t="n">
+        <v>9</v>
+      </c>
+      <c r="M21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
         <v>1</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
       <c r="Y21" t="n">
         <v>1</v>
       </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
       <c r="AC21" t="n">
         <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Registro fósil y cambios ambientales del pasado</t>
+          <t>Formación del sistema solar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1497,49 +1775,65 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10.5</v>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9</v>
       </c>
       <c r="K22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>9.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>1</v>
       </c>
-      <c r="AA22" t="n">
-        <v>1</v>
-      </c>
       <c r="AB22" t="n">
         <v>1</v>
       </c>
       <c r="AC22" t="n">
         <v>1</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1</v>
+      <c r="AF22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>Galaxias y escala del universo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1548,16 +1842,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10.5</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
         <v>7</v>
@@ -1568,26 +1865,51 @@
       <c r="M23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" t="n">
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1</v>
       </c>
       <c r="AA23" t="n">
         <v>1</v>
       </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
       <c r="AE23" t="n">
         <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1596,13 +1918,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9</v>
       </c>
       <c r="F24" t="n">
         <v>10.5</v>
       </c>
-      <c r="G24" t="n">
-        <v>8.5</v>
+      <c r="I24" t="n">
+        <v>9.5</v>
       </c>
       <c r="J24" t="n">
         <v>7</v>
@@ -1611,20 +1936,17 @@
         <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
       <c r="V24" t="n">
         <v>1</v>
       </c>
-      <c r="W24" t="n">
-        <v>1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
       <c r="Y24" t="n">
         <v>1</v>
       </c>
@@ -1636,12 +1958,25 @@
       </c>
       <c r="AC24" t="n">
         <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Impacto de las actividades humanas en los recursos</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1650,19 +1985,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M25" t="n">
         <v>7</v>
@@ -1682,20 +2017,36 @@
       <c r="X25" t="n">
         <v>1</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="AB25" t="n">
         <v>1</v>
       </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
       <c r="AE25" t="n">
         <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1710,13 +2061,13 @@
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
         <v>8</v>
       </c>
-      <c r="J26" t="n">
-        <v>7</v>
+      <c r="K26" t="n">
+        <v>8</v>
       </c>
       <c r="M26" t="n">
         <v>7</v>
@@ -1724,20 +2075,33 @@
       <c r="V26" t="n">
         <v>1</v>
       </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
       <c r="AA26" t="n">
         <v>1</v>
       </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
       <c r="AE26" t="n">
         <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tsunamis</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1748,288 +2112,293 @@
       <c r="C27" t="n">
         <v>4</v>
       </c>
-      <c r="W27" t="n">
-        <v>1</v>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>7</v>
       </c>
       <c r="Y27" t="n">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
         <v>1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Acidificación del océano</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
         <v>9</v>
       </c>
-      <c r="F29" t="n">
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
         <v>8</v>
       </c>
-      <c r="I29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J29" t="n">
-        <v>7</v>
-      </c>
-      <c r="K29" t="n">
-        <v>8</v>
-      </c>
-      <c r="M29" t="n">
-        <v>7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1</v>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Origen del universo: el Big Bang</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
-      </c>
-      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" t="n">
         <v>9</v>
-      </c>
-      <c r="F30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I30" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" t="n">
-        <v>7</v>
-      </c>
-      <c r="K30" t="n">
-        <v>8</v>
       </c>
       <c r="M30" t="n">
         <v>9.5</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
       <c r="AB30" t="n">
         <v>1</v>
       </c>
-      <c r="AC30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1</v>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" t="n">
         <v>7</v>
       </c>
       <c r="K31" t="n">
         <v>9</v>
       </c>
-      <c r="L31" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M31" t="n">
         <v>7</v>
       </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
       <c r="AE31" t="n">
         <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
         <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
         <v>8.5</v>
       </c>
-      <c r="K32" t="n">
-        <v>9</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="J32" t="n">
         <v>7</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
@@ -2038,21 +2407,40 @@
       </c>
       <c r="Y32" t="n">
         <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Recursos naturales renovables y no renovables</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>9</v>
@@ -2064,82 +2452,68 @@
         <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J33" t="n">
         <v>7</v>
       </c>
-      <c r="L33" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M33" t="n">
         <v>7</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
-      <c r="S33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
       <c r="Y33" t="n">
         <v>1</v>
       </c>
-      <c r="Z33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1</v>
-      </c>
       <c r="AC33" t="n">
         <v>1</v>
       </c>
-      <c r="AD33" t="n">
-        <v>1</v>
-      </c>
       <c r="AE33" t="n">
         <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Capas de la atmósfera y variación con la altitud</t>
+          <t>Registro fósil y cambios ambientales del pasado</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
-        <v>10.5</v>
-      </c>
       <c r="I34" t="n">
-        <v>10</v>
-      </c>
-      <c r="J34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
         <v>9</v>
@@ -2147,15 +2521,9 @@
       <c r="M34" t="n">
         <v>7</v>
       </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="n">
-        <v>1</v>
-      </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
@@ -2165,44 +2533,60 @@
       <c r="W34" t="n">
         <v>1</v>
       </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
       <c r="AA34" t="n">
         <v>1</v>
       </c>
       <c r="AB34" t="n">
         <v>1</v>
       </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
       <c r="AE34" t="n">
         <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
         <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>9</v>
-      </c>
-      <c r="F35" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>7</v>
@@ -2210,90 +2594,79 @@
       <c r="K35" t="n">
         <v>8</v>
       </c>
-      <c r="L35" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M35" t="n">
         <v>7</v>
       </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1</v>
-      </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S35" t="n">
-        <v>1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
       <c r="V35" t="n">
         <v>1</v>
       </c>
       <c r="W35" t="n">
         <v>1</v>
       </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC35" t="n">
+      <c r="AA35" t="n">
         <v>1</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ciclo de las rocas</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" t="n">
-        <v>9</v>
-      </c>
-      <c r="E36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
         <v>10.5</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
       </c>
+      <c r="K36" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
       <c r="Y36" t="n">
         <v>1</v>
       </c>
@@ -2306,54 +2679,52 @@
       <c r="AC36" t="n">
         <v>1</v>
       </c>
-      <c r="AE36" t="n">
-        <v>1</v>
+      <c r="AF36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
       </c>
-      <c r="G37" t="n">
-        <v>2</v>
-      </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" t="n">
         <v>9</v>
       </c>
-      <c r="K37" t="n">
-        <v>8</v>
-      </c>
       <c r="M37" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
@@ -2363,7 +2734,10 @@
       <c r="W37" t="n">
         <v>1</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
         <v>1</v>
       </c>
       <c r="AB37" t="n">
@@ -2371,99 +2745,83 @@
       </c>
       <c r="AE37" t="n">
         <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="n">
         <v>8</v>
       </c>
-      <c r="F38" t="n">
-        <v>8</v>
-      </c>
-      <c r="G38" t="n">
-        <v>6</v>
-      </c>
-      <c r="I38" t="n">
-        <v>9.5</v>
-      </c>
       <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="K38" t="n">
-        <v>8</v>
-      </c>
-      <c r="L38" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M38" t="n">
         <v>7</v>
       </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
-      <c r="X38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1</v>
-      </c>
       <c r="AA38" t="n">
         <v>1</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1</v>
-      </c>
       <c r="AE38" t="n">
         <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>previo</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2472,22 +2830,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
       </c>
-      <c r="G39" t="n">
-        <v>6</v>
+      <c r="I39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>9</v>
-      </c>
-      <c r="L39" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="M39" t="n">
         <v>7</v>
@@ -2495,13 +2853,10 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
         <v>1</v>
       </c>
       <c r="V39" t="n">
@@ -2510,13 +2865,10 @@
       <c r="W39" t="n">
         <v>1</v>
       </c>
-      <c r="X39" t="n">
-        <v>1</v>
-      </c>
       <c r="Y39" t="n">
         <v>1</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
@@ -2525,17 +2877,27 @@
       <c r="AC39" t="n">
         <v>1</v>
       </c>
-      <c r="AD39" t="n">
-        <v>1</v>
-      </c>
       <c r="AE39" t="n">
         <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Origen del universo: el Big Bang</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2544,42 +2906,39 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
       </c>
       <c r="F40" t="n">
         <v>10.5</v>
       </c>
-      <c r="G40" t="n">
-        <v>6</v>
-      </c>
       <c r="I40" t="n">
         <v>10</v>
       </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
       <c r="K40" t="n">
-        <v>9</v>
-      </c>
-      <c r="L40" t="n">
+        <v>8</v>
+      </c>
+      <c r="M40" t="n">
         <v>9.5</v>
       </c>
-      <c r="M40" t="n">
-        <v>7</v>
+      <c r="N40" t="n">
+        <v>1</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="n">
+      <c r="S40" t="n">
         <v>1</v>
       </c>
       <c r="V40" t="n">
@@ -2588,9 +2947,15 @@
       <c r="W40" t="n">
         <v>1</v>
       </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
       <c r="Y40" t="n">
         <v>1</v>
       </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
@@ -2600,14 +2965,27 @@
       <c r="AC40" t="n">
         <v>1</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1</v>
+      <c r="AD40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2616,25 +2994,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
-      </c>
-      <c r="I41" t="n">
-        <v>8</v>
-      </c>
-      <c r="J41" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M41" t="n">
         <v>7</v>
@@ -2645,9 +3017,6 @@
       <c r="T41" t="n">
         <v>1</v>
       </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
@@ -2657,20 +3026,24 @@
       <c r="Y41" t="n">
         <v>1</v>
       </c>
-      <c r="AB41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1</v>
+      <c r="AF41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2679,16 +3052,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F42" t="n">
         <v>8</v>
       </c>
       <c r="G42" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9.5</v>
       </c>
       <c r="M42" t="n">
         <v>7</v>
@@ -2696,23 +3078,63 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
       <c r="W42" t="n">
         <v>1</v>
       </c>
-      <c r="X42" t="n">
-        <v>1</v>
-      </c>
       <c r="Y42" t="n">
         <v>1</v>
       </c>
+      <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1</v>
+      </c>
       <c r="AE42" t="n">
         <v>1</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Capas de la atmósfera y variación con la altitud</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2724,25 +3146,68 @@
         <v>3</v>
       </c>
       <c r="D43" t="n">
+        <v>9</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I43" t="n">
         <v>10</v>
       </c>
-      <c r="F43" t="n">
-        <v>8</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" t="n">
+        <v>9</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
         <v>3</v>
       </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1</v>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>no_retomado</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2751,19 +3216,55 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
         <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" t="n">
+        <v>10</v>
       </c>
       <c r="J44" t="n">
         <v>7</v>
       </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M44" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
       <c r="V44" t="n">
         <v>1</v>
@@ -2771,23 +3272,39 @@
       <c r="W44" t="n">
         <v>1</v>
       </c>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
       <c r="Y44" t="n">
         <v>1</v>
       </c>
-      <c r="AA44" t="n">
-        <v>1</v>
-      </c>
       <c r="AB44" t="n">
         <v>1</v>
       </c>
       <c r="AC44" t="n">
         <v>1</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Eclipses solares y lunares</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2796,31 +3313,86 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
         <v>8</v>
       </c>
+      <c r="L45" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M45" t="n">
         <v>7</v>
       </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1</v>
+      </c>
       <c r="AB45" t="n">
         <v>1</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2829,25 +3401,28 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D46" t="n">
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F46" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L46" t="n">
         <v>9.5</v>
@@ -2855,9 +3430,6 @@
       <c r="M46" t="n">
         <v>7</v>
       </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
@@ -2867,9 +3439,6 @@
       <c r="R46" t="n">
         <v>1</v>
       </c>
-      <c r="S46" t="n">
-        <v>1</v>
-      </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
@@ -2891,17 +3460,39 @@
       <c r="Z46" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
       <c r="AB46" t="n">
         <v>1</v>
       </c>
       <c r="AC46" t="n">
         <v>1</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2910,19 +3501,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
         <v>9</v>
       </c>
-      <c r="E47" t="n">
-        <v>4</v>
-      </c>
       <c r="F47" t="n">
         <v>8</v>
       </c>
-      <c r="I47" t="n">
-        <v>4</v>
+      <c r="G47" t="n">
+        <v>6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>9</v>
+      </c>
+      <c r="L47" t="n">
+        <v>9.5</v>
       </c>
       <c r="M47" t="n">
         <v>7</v>
@@ -2930,7 +3524,13 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="R47" t="n">
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
         <v>1</v>
       </c>
       <c r="V47" t="n">
@@ -2945,7 +3545,7 @@
       <c r="Y47" t="n">
         <v>1</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="Z47" t="n">
         <v>1</v>
       </c>
       <c r="AB47" t="n">
@@ -2954,14 +3554,30 @@
       <c r="AC47" t="n">
         <v>1</v>
       </c>
+      <c r="AD47" t="n">
+        <v>1</v>
+      </c>
       <c r="AE47" t="n">
         <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2970,10 +3586,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8</v>
       </c>
       <c r="J48" t="n">
         <v>7</v>
@@ -2982,7 +3607,13 @@
         <v>8</v>
       </c>
       <c r="M48" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
       </c>
       <c r="V48" t="n">
         <v>1</v>
@@ -3004,12 +3635,25 @@
       </c>
       <c r="AE48" t="n">
         <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fósiles y su formación</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3018,7 +3662,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
         <v>9</v>
@@ -3026,56 +3670,33 @@
       <c r="F49" t="n">
         <v>8</v>
       </c>
-      <c r="G49" t="n">
-        <v>2</v>
-      </c>
       <c r="I49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1</v>
-      </c>
       <c r="Y49" t="n">
         <v>1</v>
       </c>
-      <c r="Z49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1</v>
+      <c r="AF49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Deriva continental y expansión del fondo oceánico</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3084,70 +3705,56 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8</v>
-      </c>
-      <c r="G50" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I50" t="n">
+        <v>9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>7</v>
+      </c>
+      <c r="M50" t="n">
         <v>9.5</v>
       </c>
-      <c r="J50" t="n">
-        <v>9</v>
-      </c>
-      <c r="K50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M50" t="n">
-        <v>7</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1</v>
-      </c>
       <c r="V50" t="n">
         <v>1</v>
       </c>
       <c r="W50" t="n">
         <v>1</v>
       </c>
-      <c r="X50" t="n">
-        <v>1</v>
-      </c>
       <c r="Y50" t="n">
         <v>1</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB50" t="n">
         <v>1</v>
       </c>
       <c r="AC50" t="n">
         <v>1</v>
       </c>
-      <c r="AD50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1</v>
+      <c r="AF50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3156,39 +3763,69 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="n">
         <v>9</v>
       </c>
       <c r="F51" t="n">
         <v>10.5</v>
       </c>
+      <c r="G51" t="n">
+        <v>8.5</v>
+      </c>
       <c r="I51" t="n">
+        <v>10</v>
+      </c>
+      <c r="J51" t="n">
+        <v>9</v>
+      </c>
+      <c r="K51" t="n">
+        <v>9</v>
+      </c>
+      <c r="L51" t="n">
         <v>9.5</v>
       </c>
-      <c r="J51" t="n">
-        <v>7</v>
-      </c>
-      <c r="K51" t="n">
-        <v>8</v>
-      </c>
       <c r="M51" t="n">
         <v>7</v>
       </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
       <c r="R51" t="n">
         <v>1</v>
       </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
       <c r="V51" t="n">
         <v>1</v>
       </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
       <c r="Y51" t="n">
         <v>1</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="Z51" t="n">
         <v>1</v>
       </c>
       <c r="AB51" t="n">
@@ -3196,12 +3833,25 @@
       </c>
       <c r="AC51" t="n">
         <v>1</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>no_retomado</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3210,28 +3860,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
         <v>9</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
         <v>8</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
-      </c>
-      <c r="J52" t="n">
-        <v>7</v>
-      </c>
-      <c r="K52" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -3239,9 +3883,6 @@
       <c r="R52" t="n">
         <v>1</v>
       </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
       <c r="V52" t="n">
         <v>1</v>
       </c>
@@ -3254,14 +3895,36 @@
       <c r="Y52" t="n">
         <v>1</v>
       </c>
+      <c r="AA52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
       <c r="AE52" t="n">
         <v>1</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3270,37 +3933,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
         <v>9</v>
       </c>
-      <c r="F53" t="n">
+      <c r="J53" t="n">
+        <v>7</v>
+      </c>
+      <c r="K53" t="n">
         <v>8</v>
       </c>
-      <c r="I53" t="n">
-        <v>7</v>
-      </c>
-      <c r="J53" t="n">
-        <v>7</v>
-      </c>
-      <c r="K53" t="n">
-        <v>9</v>
-      </c>
       <c r="M53" t="n">
-        <v>7</v>
-      </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>1</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="V53" t="n">
         <v>1</v>
@@ -3308,20 +3953,39 @@
       <c r="W53" t="n">
         <v>1</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="X53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="n">
         <v>1</v>
       </c>
       <c r="AB53" t="n">
         <v>1</v>
       </c>
+      <c r="AC53" t="n">
+        <v>1</v>
+      </c>
       <c r="AE53" t="n">
         <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Límites de placas: convergentes, divergentes y transformantes</t>
+          <t>Fósiles y su formación</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3330,22 +3994,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
         <v>9</v>
       </c>
-      <c r="E54" t="n">
-        <v>7</v>
-      </c>
       <c r="F54" t="n">
         <v>8</v>
       </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M54" t="n">
         <v>7</v>
@@ -3353,26 +4017,54 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
       <c r="R54" t="n">
         <v>1</v>
       </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
       <c r="V54" t="n">
         <v>1</v>
       </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
       <c r="Y54" t="n">
         <v>1</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" t="n">
         <v>1</v>
       </c>
       <c r="AC54" t="n">
         <v>1</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mareas</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3381,19 +4073,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
         <v>9</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" t="n">
         <v>6</v>
       </c>
-      <c r="F55" t="n">
-        <v>10.5</v>
-      </c>
       <c r="I55" t="n">
-        <v>9.5</v>
+        <v>8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>8</v>
       </c>
       <c r="M55" t="n">
         <v>7</v>
@@ -3401,26 +4099,57 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
       <c r="R55" t="n">
         <v>1</v>
       </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
       <c r="V55" t="n">
         <v>1</v>
       </c>
-      <c r="AA55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB55" t="n">
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD55" t="n">
         <v>1</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3429,40 +4158,71 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
         <v>9</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
+      </c>
+      <c r="I56" t="n">
+        <v>10</v>
       </c>
       <c r="J56" t="n">
         <v>7</v>
       </c>
+      <c r="K56" t="n">
+        <v>9</v>
+      </c>
+      <c r="M56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
+      <c r="X56" t="n">
+        <v>1</v>
+      </c>
       <c r="Y56" t="n">
         <v>1</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1</v>
-      </c>
       <c r="AE56" t="n">
         <v>1</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oleaje, dinámica costera y sedimentación marina</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3471,13 +4231,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
         <v>9</v>
       </c>
       <c r="F57" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>7</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" t="n">
+        <v>9</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
@@ -3485,10 +4254,19 @@
       <c r="O57" t="n">
         <v>1</v>
       </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
@@ -3496,12 +4274,28 @@
       </c>
       <c r="AB57" t="n">
         <v>1</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ondas sísmicas, magnitud e intensidad</t>
+          <t>Límites de placas: convergentes, divergentes y transformantes</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3515,14 +4309,20 @@
       <c r="D58" t="n">
         <v>9</v>
       </c>
+      <c r="E58" t="n">
+        <v>7</v>
+      </c>
       <c r="F58" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7</v>
       </c>
       <c r="M58" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -3533,29 +4333,33 @@
       <c r="V58" t="n">
         <v>1</v>
       </c>
-      <c r="W58" t="n">
-        <v>1</v>
-      </c>
       <c r="Y58" t="n">
         <v>1</v>
       </c>
       <c r="AA58" t="n">
         <v>1</v>
       </c>
-      <c r="AB58" t="n">
-        <v>1</v>
-      </c>
       <c r="AC58" t="n">
         <v>1</v>
       </c>
-      <c r="AE58" t="n">
-        <v>1</v>
+      <c r="AF58" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Origen del magma y vulcanismo</t>
+          <t>Mareas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3569,14 +4373,14 @@
       <c r="D59" t="n">
         <v>9</v>
       </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
       <c r="F59" t="n">
         <v>10.5</v>
       </c>
       <c r="I59" t="n">
-        <v>6</v>
-      </c>
-      <c r="J59" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="M59" t="n">
         <v>7</v>
@@ -3590,29 +4394,33 @@
       <c r="V59" t="n">
         <v>1</v>
       </c>
-      <c r="W59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1</v>
-      </c>
       <c r="AA59" t="n">
         <v>1</v>
       </c>
       <c r="AB59" t="n">
         <v>1</v>
       </c>
-      <c r="AC59" t="n">
-        <v>1</v>
-      </c>
       <c r="AE59" t="n">
         <v>1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Ondas sísmicas, magnitud e intensidad</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3621,37 +4429,65 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" t="n">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="F60" t="n">
+        <v>10.5</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
-      </c>
-      <c r="K60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M60" t="n">
-        <v>7</v>
-      </c>
-      <c r="T60" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC60" t="n">
         <v>1</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Planetas: tipos y comparación</t>
+          <t>Origen del magma y vulcanismo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3668,18 +4504,12 @@
       <c r="F61" t="n">
         <v>10.5</v>
       </c>
-      <c r="G61" t="n">
-        <v>8.5</v>
-      </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J61" t="n">
         <v>7</v>
       </c>
-      <c r="K61" t="n">
-        <v>8</v>
-      </c>
       <c r="M61" t="n">
         <v>7</v>
       </c>
@@ -3692,7 +4522,7 @@
       <c r="V61" t="n">
         <v>1</v>
       </c>
-      <c r="X61" t="n">
+      <c r="W61" t="n">
         <v>1</v>
       </c>
       <c r="Y61" t="n">
@@ -3706,12 +4536,28 @@
       </c>
       <c r="AC61" t="n">
         <v>1</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Planetas: tipos y comparación</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3720,52 +4566,71 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G62" t="n">
         <v>8.5</v>
       </c>
+      <c r="I62" t="n">
+        <v>8</v>
+      </c>
+      <c r="J62" t="n">
+        <v>7</v>
+      </c>
+      <c r="K62" t="n">
+        <v>8</v>
+      </c>
       <c r="M62" t="n">
         <v>7</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="P62" t="n">
+      <c r="R62" t="n">
         <v>1</v>
       </c>
       <c r="V62" t="n">
         <v>1</v>
       </c>
-      <c r="W62" t="n">
-        <v>1</v>
-      </c>
       <c r="X62" t="n">
         <v>1</v>
       </c>
       <c r="Y62" t="n">
         <v>1</v>
       </c>
-      <c r="Z62" t="n">
+      <c r="AA62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" t="n">
         <v>1</v>
       </c>
       <c r="AC62" t="n">
         <v>1</v>
       </c>
-      <c r="AE62" t="n">
-        <v>1</v>
+      <c r="AF62" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3774,28 +4639,65 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
+      <c r="X63" t="n">
+        <v>1</v>
+      </c>
       <c r="Y63" t="n">
         <v>1</v>
       </c>
+      <c r="Z63" t="n">
+        <v>1</v>
+      </c>
       <c r="AC63" t="n">
         <v>1</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>El océano: propiedades del agua de mar y zonas</t>
+          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3804,46 +4706,41 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
         <v>9</v>
       </c>
-      <c r="F64" t="n">
-        <v>8</v>
-      </c>
-      <c r="I64" t="n">
-        <v>10</v>
-      </c>
-      <c r="J64" t="n">
-        <v>7</v>
-      </c>
-      <c r="M64" t="n">
-        <v>7</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB64" t="n">
+      <c r="W64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC64" t="n">
         <v>1</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
+          <t>El océano: propiedades del agua de mar y zonas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3852,76 +4749,59 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
         <v>9</v>
       </c>
-      <c r="E65" t="n">
-        <v>9</v>
-      </c>
       <c r="F65" t="n">
         <v>8</v>
       </c>
-      <c r="G65" t="n">
-        <v>8.5</v>
-      </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J65" t="n">
         <v>7</v>
       </c>
-      <c r="K65" t="n">
-        <v>8</v>
-      </c>
       <c r="M65" t="n">
         <v>7</v>
       </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
       <c r="R65" t="n">
         <v>1</v>
       </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1</v>
-      </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
-      <c r="W65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1</v>
-      </c>
       <c r="AA65" t="n">
         <v>1</v>
       </c>
       <c r="AB65" t="n">
         <v>1</v>
       </c>
-      <c r="AC65" t="n">
-        <v>1</v>
-      </c>
       <c r="AE65" t="n">
         <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Recursos naturales renovables y no renovables</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3930,49 +4810,83 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="E66" t="n">
+        <v>9</v>
       </c>
       <c r="F66" t="n">
         <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I66" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="J66" t="n">
         <v>7</v>
       </c>
+      <c r="K66" t="n">
+        <v>8</v>
+      </c>
       <c r="M66" t="n">
         <v>7</v>
       </c>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
       <c r="O66" t="n">
         <v>1</v>
       </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
       <c r="R66" t="n">
         <v>1</v>
       </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
       <c r="W66" t="n">
         <v>1</v>
       </c>
-      <c r="X66" t="n">
-        <v>1</v>
-      </c>
       <c r="Y66" t="n">
         <v>1</v>
       </c>
+      <c r="AA66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1</v>
+      </c>
       <c r="AC66" t="n">
         <v>1</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4031,6 +4945,19 @@
       <c r="AE67" t="n">
         <v>1</v>
       </c>
+      <c r="AF67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4052,6 +4979,19 @@
       <c r="AB68" t="n">
         <v>1</v>
       </c>
+      <c r="AF68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4106,6 +5046,19 @@
       <c r="AC69" t="n">
         <v>1</v>
       </c>
+      <c r="AF69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4172,6 +5125,19 @@
       <c r="AE70" t="n">
         <v>1</v>
       </c>
+      <c r="AF70" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4247,6 +5213,19 @@
       <c r="AE71" t="n">
         <v>1</v>
       </c>
+      <c r="AF71" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4263,7 +5242,7 @@
         <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E72" t="n">
         <v>2</v>
@@ -4295,6 +5274,19 @@
       <c r="AC72" t="n">
         <v>1</v>
       </c>
+      <c r="AF72" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4358,6 +5350,19 @@
       <c r="AE73" t="n">
         <v>1</v>
       </c>
+      <c r="AF73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4412,6 +5417,19 @@
       <c r="AE74" t="n">
         <v>1</v>
       </c>
+      <c r="AF74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4469,6 +5487,19 @@
       <c r="AE75" t="n">
         <v>1</v>
       </c>
+      <c r="AF75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4529,6 +5560,19 @@
       <c r="AE76" t="n">
         <v>1</v>
       </c>
+      <c r="AF76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4542,7 +5586,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
         <v>11</v>
@@ -4565,6 +5609,19 @@
       <c r="AE77" t="n">
         <v>1</v>
       </c>
+      <c r="AF77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4604,6 +5661,19 @@
       <c r="AC78" t="n">
         <v>1</v>
       </c>
+      <c r="AF78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>retomado</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4622,6 +5692,19 @@
       <c r="D79" t="n">
         <v>9</v>
       </c>
+      <c r="AF79" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4639,6 +5722,19 @@
       </c>
       <c r="D80" t="n">
         <v>9</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8039,7 +9135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8159,11 +9255,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>COUNTIF(Datos!B2:B80,A11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B11">
-        <f>SUM(B2:B10)</f>
+      <c r="B12">
+        <f>SUM(B2:B11)</f>
         <v/>
       </c>
     </row>

--- a/internacional/Contraste_tierra_espacio.xlsx
+++ b/internacional/Contraste_tierra_espacio.xlsx
@@ -676,116 +676,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Acidificación del océano</t>
+          <t>Convección del manto y energía interna de la Tierra</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
         <v>9</v>
       </c>
-      <c r="F3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9</v>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Energía geotérmica</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7</v>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -794,60 +758,42 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>10.5</v>
       </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>10</v>
-      </c>
       <c r="K5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>9.5</v>
       </c>
-      <c r="M5" t="n">
-        <v>7</v>
-      </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
@@ -857,21 +803,12 @@
       <c r="Y5" t="n">
         <v>1</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1</v>
-      </c>
       <c r="AB5" t="n">
         <v>1</v>
       </c>
       <c r="AC5" t="n">
         <v>1</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>3</v>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -879,38 +816,23 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Convección del manto y energía interna de la Tierra</t>
+          <t>Tsunamis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>9</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
@@ -918,18 +840,12 @@
       <c r="Y6" t="n">
         <v>1</v>
       </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
       <c r="AB6" t="n">
         <v>1</v>
       </c>
-      <c r="AC6" t="n">
-        <v>1</v>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -941,43 +857,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oleaje, dinámica costera y sedimentación marina</t>
+          <t>Aguas subterráneas y acuíferos</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
       <c r="Y7" t="n">
         <v>1</v>
       </c>
-      <c r="AA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -986,91 +896,136 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Energía geotérmica</t>
+          <t>Capas internas de la Tierra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
         <v>10</v>
       </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" t="n">
         <v>1</v>
       </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
       <c r="AC8" t="n">
         <v>1</v>
       </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3</v>
+      </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
+          <t>Ciclo de las rocas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
       </c>
       <c r="F9" t="n">
         <v>10.5</v>
       </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
-      <c r="M9" t="n">
-        <v>9.5</v>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>1</v>
       </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
       <c r="AB9" t="n">
         <v>1</v>
       </c>
       <c r="AC9" t="n">
         <v>1</v>
       </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3</v>
+      </c>
       <c r="AG9" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -1078,48 +1033,60 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tsunamis</t>
+          <t>Ciclones tropicales y tormentas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
+      <c r="AF10" t="n">
+        <v>4</v>
+      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
           <t>previo</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aguas subterráneas y acuíferos</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1136,20 +1103,29 @@
       <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="I11" t="n">
-        <v>3</v>
+      <c r="G11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" t="n">
         <v>1</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -1165,7 +1141,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Capas internas de la Tierra</t>
+          <t>Eclipses solares y lunares</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,59 +1150,32 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
         <v>8</v>
       </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
       <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
       <c r="AB12" t="n">
         <v>1</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
       <c r="AF12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -1238,7 +1187,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ciclo de las rocas</t>
+          <t>El Sol como estrella</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1247,27 +1196,30 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
@@ -1282,11 +1234,8 @@
       <c r="AC13" t="n">
         <v>1</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
       <c r="AF13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -1302,7 +1251,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciclones tropicales y tormentas</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1313,30 +1262,60 @@
       <c r="C14" t="n">
         <v>4</v>
       </c>
-      <c r="D14" t="n">
-        <v>11</v>
+      <c r="F14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
       </c>
       <c r="M14" t="n">
         <v>7</v>
       </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
       <c r="V14" t="n">
         <v>1</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1</v>
       </c>
       <c r="AB14" t="n">
         <v>1</v>
       </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -1348,7 +1327,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>Ciclo de vida de las estrellas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1357,41 +1336,50 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" t="n">
         <v>8</v>
       </c>
-      <c r="G15" t="n">
-        <v>8.5</v>
-      </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="W15" t="n">
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
         <v>1</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -1403,7 +1391,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Eclipses solares y lunares</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1415,10 +1403,10 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
-      </c>
-      <c r="E16" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>7</v>
@@ -1429,7 +1417,7 @@
       <c r="M16" t="n">
         <v>7</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AE16" t="n">
         <v>1</v>
       </c>
       <c r="AF16" t="n">
@@ -1449,7 +1437,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>El Sol como estrella</t>
+          <t>Formación y evolución temprana de la Tierra</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1458,25 +1446,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I17" t="n">
         <v>10</v>
       </c>
-      <c r="G17" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
       <c r="J17" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>9.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -1484,24 +1469,30 @@
       <c r="S17" t="n">
         <v>1</v>
       </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
       <c r="Y17" t="n">
         <v>1</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
       <c r="AB17" t="n">
         <v>1</v>
       </c>
       <c r="AC17" t="n">
         <v>1</v>
       </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -1513,7 +1504,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Formación del sistema solar</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1527,20 +1518,17 @@
       <c r="F18" t="n">
         <v>10.5</v>
       </c>
-      <c r="G18" t="n">
-        <v>6</v>
-      </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
         <v>8</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1560,16 +1548,10 @@
       <c r="Y18" t="n">
         <v>1</v>
       </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
       <c r="AB18" t="n">
         <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE18" t="n">
         <v>1</v>
       </c>
       <c r="AF18" t="n">
@@ -1589,7 +1571,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las estrellas</t>
+          <t>Galaxias y escala del universo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1598,30 +1580,42 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9</v>
       </c>
       <c r="F19" t="n">
         <v>10.5</v>
       </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
         <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
       <c r="V19" t="n">
         <v>1</v>
       </c>
       <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1</v>
       </c>
       <c r="AA19" t="n">
@@ -1641,7 +1635,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -1653,7 +1647,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1662,13 +1656,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
+      <c r="F20" t="n">
+        <v>10.5</v>
+      </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J20" t="n">
         <v>7</v>
@@ -1679,11 +1676,29 @@
       <c r="M20" t="n">
         <v>7</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -1699,7 +1714,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Formación y evolución temprana de la Tierra</t>
+          <t>Impacto de las actividades humanas en los recursos</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1708,27 +1723,27 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
@@ -1737,6 +1752,9 @@
       <c r="W21" t="n">
         <v>1</v>
       </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
       <c r="Y21" t="n">
         <v>1</v>
       </c>
@@ -1750,11 +1768,11 @@
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -1766,7 +1784,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Formación del sistema solar</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1775,49 +1793,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>10.5</v>
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
         <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AA22" t="n">
         <v>1</v>
       </c>
       <c r="AC22" t="n">
         <v>1</v>
       </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
       <c r="AF22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -1833,7 +1839,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Galaxias y escala del universo</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1844,60 +1850,30 @@
       <c r="C23" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="n">
-        <v>11</v>
-      </c>
-      <c r="E23" t="n">
-        <v>9</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>7</v>
       </c>
-      <c r="K23" t="n">
-        <v>8</v>
-      </c>
       <c r="M23" t="n">
         <v>7</v>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
       <c r="Y23" t="n">
         <v>1</v>
       </c>
-      <c r="AA23" t="n">
-        <v>1</v>
-      </c>
       <c r="AB23" t="n">
         <v>1</v>
       </c>
       <c r="AC23" t="n">
         <v>1</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
       <c r="AF23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -1909,7 +1885,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1918,13 +1894,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
         <v>9.5</v>
@@ -1932,19 +1908,13 @@
       <c r="J24" t="n">
         <v>7</v>
       </c>
-      <c r="K24" t="n">
-        <v>8</v>
-      </c>
-      <c r="M24" t="n">
-        <v>7</v>
-      </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
@@ -1953,18 +1923,15 @@
       <c r="AA24" t="n">
         <v>1</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1</v>
-      </c>
       <c r="AC24" t="n">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -1976,7 +1943,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Impacto de las actividades humanas en los recursos</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1985,52 +1952,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
         <v>9</v>
       </c>
-      <c r="F25" t="n">
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
         <v>8</v>
-      </c>
-      <c r="I25" t="n">
-        <v>8</v>
-      </c>
-      <c r="K25" t="n">
-        <v>8</v>
-      </c>
-      <c r="M25" t="n">
-        <v>7</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -2046,7 +1998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2055,30 +2007,36 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>7</v>
+        <v>9.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
       </c>
       <c r="V26" t="n">
         <v>1</v>
       </c>
-      <c r="AA26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AB26" t="n">
         <v>1</v>
       </c>
       <c r="AE26" t="n">
@@ -2089,7 +2047,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -2101,7 +2059,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2110,32 +2068,38 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>9</v>
       </c>
       <c r="M27" t="n">
         <v>7</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC27" t="n">
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -2147,7 +2111,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2156,16 +2120,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
-      <c r="I28" t="n">
-        <v>9.5</v>
+      <c r="G28" t="n">
+        <v>8.5</v>
       </c>
       <c r="J28" t="n">
         <v>7</v>
@@ -2173,27 +2137,27 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
       <c r="Y28" t="n">
         <v>1</v>
       </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
       <c r="AC28" t="n">
         <v>1</v>
       </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
       <c r="AF28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -2205,7 +2169,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>Recursos naturales renovables y no renovables</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2214,29 +2178,44 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>9</v>
       </c>
-      <c r="E29" t="n">
-        <v>2</v>
+      <c r="F29" t="n">
+        <v>8</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
       </c>
+      <c r="I29" t="n">
+        <v>9.5</v>
+      </c>
       <c r="J29" t="n">
         <v>7</v>
       </c>
+      <c r="M29" t="n">
+        <v>7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
       <c r="Y29" t="n">
         <v>1</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1</v>
-      </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
@@ -2244,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2260,7 +2239,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Registro fósil y cambios ambientales del pasado</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2269,27 +2248,18 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
         <v>9</v>
       </c>
       <c r="M30" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O30" t="n">
+        <v>7</v>
+      </c>
+      <c r="R30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
@@ -2298,18 +2268,30 @@
       <c r="V30" t="n">
         <v>1</v>
       </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
       <c r="AB30" t="n">
         <v>1</v>
       </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
       <c r="AE30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -2321,7 +2303,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2339,18 +2321,30 @@
         <v>2</v>
       </c>
       <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
         <v>2</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
         <v>7</v>
       </c>
-      <c r="T31" t="n">
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>1</v>
       </c>
       <c r="AE31" t="n">
@@ -2373,7 +2367,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2382,13 +2376,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G32" t="n">
         <v>8.5</v>
@@ -2396,9 +2387,18 @@
       <c r="J32" t="n">
         <v>7</v>
       </c>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
+      <c r="M32" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
@@ -2408,18 +2408,21 @@
       <c r="Y32" t="n">
         <v>1</v>
       </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
       <c r="AC32" t="n">
         <v>1</v>
       </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
       <c r="AF32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -2431,7 +2434,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Recursos naturales renovables y no renovables</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2440,30 +2443,27 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
       </c>
-      <c r="G33" t="n">
-        <v>6</v>
-      </c>
       <c r="I33" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
         <v>7</v>
       </c>
+      <c r="K33" t="n">
+        <v>9</v>
+      </c>
       <c r="M33" t="n">
         <v>7</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="V33" t="n">
@@ -2475,21 +2475,21 @@
       <c r="X33" t="n">
         <v>1</v>
       </c>
-      <c r="Y33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC33" t="n">
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -2501,7 +2501,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Registro fósil y cambios ambientales del pasado</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2510,50 +2510,44 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" t="n">
         <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
       </c>
       <c r="M34" t="n">
         <v>7</v>
       </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
-      <c r="Y34" t="n">
-        <v>1</v>
-      </c>
       <c r="AA34" t="n">
         <v>1</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1</v>
-      </c>
       <c r="AE34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -2565,28 +2559,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>7</v>
@@ -2597,16 +2588,31 @@
       <c r="M35" t="n">
         <v>7</v>
       </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
       <c r="V35" t="n">
         <v>1</v>
       </c>
       <c r="W35" t="n">
         <v>1</v>
       </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
       <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1</v>
       </c>
       <c r="AE35" t="n">
@@ -2622,29 +2628,35 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Origen del universo: el Big Bang</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9</v>
       </c>
       <c r="F36" t="n">
         <v>10.5</v>
       </c>
-      <c r="G36" t="n">
-        <v>8.5</v>
+      <c r="I36" t="n">
+        <v>10</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
@@ -2655,9 +2667,18 @@
       <c r="M36" t="n">
         <v>9.5</v>
       </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
       <c r="V36" t="n">
         <v>1</v>
       </c>
@@ -2670,6 +2691,9 @@
       <c r="Y36" t="n">
         <v>1</v>
       </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
       <c r="AA36" t="n">
         <v>1</v>
       </c>
@@ -2679,39 +2703,51 @@
       <c r="AC36" t="n">
         <v>1</v>
       </c>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
       <c r="AF36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
       </c>
+      <c r="G37" t="n">
+        <v>6</v>
+      </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J37" t="n">
         <v>7</v>
@@ -2719,15 +2755,33 @@
       <c r="K37" t="n">
         <v>9</v>
       </c>
+      <c r="L37" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M37" t="n">
         <v>7</v>
       </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
@@ -2737,75 +2791,69 @@
       <c r="X37" t="n">
         <v>1</v>
       </c>
-      <c r="AA37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1</v>
-      </c>
       <c r="AE37" t="n">
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
         <v>10</v>
       </c>
-      <c r="E38" t="n">
-        <v>5</v>
+      <c r="F38" t="n">
+        <v>10.5</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" t="n">
-        <v>8</v>
-      </c>
-      <c r="J38" t="n">
-        <v>7</v>
+        <v>8.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>9</v>
       </c>
       <c r="M38" t="n">
         <v>7</v>
       </c>
-      <c r="V38" t="n">
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
-      <c r="AA38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE38" t="n">
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -2814,14 +2862,14 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2830,7 +2878,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
         <v>9</v>
@@ -2838,14 +2886,17 @@
       <c r="F39" t="n">
         <v>8</v>
       </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
         <v>7</v>
       </c>
-      <c r="K39" t="n">
-        <v>8</v>
+      <c r="L39" t="n">
+        <v>9.5</v>
       </c>
       <c r="M39" t="n">
         <v>7</v>
@@ -2853,12 +2904,18 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
@@ -2868,6 +2925,9 @@
       <c r="Y39" t="n">
         <v>1</v>
       </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
       <c r="AA39" t="n">
         <v>1</v>
       </c>
@@ -2877,11 +2937,14 @@
       <c r="AC39" t="n">
         <v>1</v>
       </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
       <c r="AE39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -2897,7 +2960,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Origen del universo: el Big Bang</t>
+          <t>Capas de la atmósfera y variación con la altitud</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2906,12 +2969,9 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
-      </c>
-      <c r="E40" t="n">
         <v>9</v>
       </c>
       <c r="F40" t="n">
@@ -2924,13 +2984,10 @@
         <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M40" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -2941,35 +2998,26 @@
       <c r="S40" t="n">
         <v>1</v>
       </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
       <c r="V40" t="n">
         <v>1</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1</v>
-      </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
       <c r="AB40" t="n">
         <v>1</v>
       </c>
-      <c r="AC40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -2978,14 +3026,14 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2994,29 +3042,59 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D41" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" t="n">
         <v>10</v>
       </c>
-      <c r="F41" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G41" t="n">
-        <v>8.5</v>
+      <c r="J41" t="n">
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="L41" t="n">
+        <v>9.5</v>
       </c>
       <c r="M41" t="n">
         <v>7</v>
       </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
@@ -3024,6 +3102,15 @@
         <v>1</v>
       </c>
       <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1</v>
       </c>
       <c r="AF41" t="n">
@@ -3043,7 +3130,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3052,22 +3139,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
         <v>9</v>
       </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
       <c r="F42" t="n">
         <v>8</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="K42" t="n">
+        <v>8</v>
       </c>
       <c r="L42" t="n">
         <v>9.5</v>
@@ -3081,12 +3174,12 @@
       <c r="P42" t="n">
         <v>1</v>
       </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
       <c r="S42" t="n">
         <v>1</v>
       </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
       <c r="U42" t="n">
         <v>1</v>
       </c>
@@ -3099,18 +3192,9 @@
       <c r="Y42" t="n">
         <v>1</v>
       </c>
-      <c r="Z42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1</v>
-      </c>
       <c r="AB42" t="n">
         <v>1</v>
       </c>
-      <c r="AC42" t="n">
-        <v>1</v>
-      </c>
       <c r="AD42" t="n">
         <v>1</v>
       </c>
@@ -3118,7 +3202,7 @@
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3134,7 +3218,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Capas de la atmósfera y variación con la altitud</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3143,22 +3227,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
         <v>9</v>
       </c>
+      <c r="E43" t="n">
+        <v>8</v>
+      </c>
       <c r="F43" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="L43" t="n">
+        <v>9.5</v>
       </c>
       <c r="M43" t="n">
         <v>7</v>
@@ -3166,32 +3259,50 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
       <c r="R43" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="n">
-        <v>1</v>
-      </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1</v>
+      </c>
       <c r="AA43" t="n">
         <v>1</v>
       </c>
       <c r="AB43" t="n">
         <v>1</v>
       </c>
+      <c r="AC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1</v>
+      </c>
       <c r="AE43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3200,14 +3311,14 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3221,23 +3332,14 @@
       <c r="D44" t="n">
         <v>9</v>
       </c>
-      <c r="E44" t="n">
-        <v>9</v>
-      </c>
       <c r="F44" t="n">
         <v>8</v>
       </c>
       <c r="G44" t="n">
         <v>6</v>
       </c>
-      <c r="I44" t="n">
-        <v>10</v>
-      </c>
-      <c r="J44" t="n">
-        <v>7</v>
-      </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L44" t="n">
         <v>9.5</v>
@@ -3245,21 +3347,12 @@
       <c r="M44" t="n">
         <v>7</v>
       </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1</v>
-      </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
@@ -3278,10 +3371,16 @@
       <c r="Y44" t="n">
         <v>1</v>
       </c>
+      <c r="Z44" t="n">
+        <v>1</v>
+      </c>
       <c r="AB44" t="n">
         <v>1</v>
       </c>
       <c r="AC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1</v>
       </c>
       <c r="AE44" t="n">
@@ -3304,7 +3403,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3313,28 +3412,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10</v>
+      </c>
+      <c r="K45" t="n">
         <v>9</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" t="n">
-        <v>8</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" t="n">
-        <v>9</v>
-      </c>
-      <c r="K45" t="n">
-        <v>8</v>
       </c>
       <c r="L45" t="n">
         <v>9.5</v>
@@ -3348,7 +3441,7 @@
       <c r="P45" t="n">
         <v>1</v>
       </c>
-      <c r="S45" t="n">
+      <c r="R45" t="n">
         <v>1</v>
       </c>
       <c r="T45" t="n">
@@ -3366,10 +3459,13 @@
       <c r="Y45" t="n">
         <v>1</v>
       </c>
+      <c r="AA45" t="n">
+        <v>1</v>
+      </c>
       <c r="AB45" t="n">
         <v>1</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AC45" t="n">
         <v>1</v>
       </c>
       <c r="AE45" t="n">
@@ -3385,14 +3481,14 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3401,13 +3497,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
-      </c>
-      <c r="E46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F46" t="n">
         <v>8</v>
@@ -3416,7 +3509,7 @@
         <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
         <v>7</v>
@@ -3424,27 +3517,15 @@
       <c r="K46" t="n">
         <v>8</v>
       </c>
-      <c r="L46" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M46" t="n">
         <v>7</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
-      <c r="U46" t="n">
-        <v>1</v>
-      </c>
       <c r="V46" t="n">
         <v>1</v>
       </c>
@@ -3457,26 +3538,17 @@
       <c r="Y46" t="n">
         <v>1</v>
       </c>
-      <c r="Z46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1</v>
-      </c>
       <c r="AB46" t="n">
         <v>1</v>
       </c>
       <c r="AC46" t="n">
         <v>1</v>
       </c>
-      <c r="AD46" t="n">
-        <v>1</v>
-      </c>
       <c r="AE46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3492,7 +3564,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3501,7 +3573,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
         <v>9</v>
@@ -3509,59 +3581,17 @@
       <c r="F47" t="n">
         <v>8</v>
       </c>
-      <c r="G47" t="n">
-        <v>6</v>
-      </c>
-      <c r="K47" t="n">
-        <v>9</v>
-      </c>
-      <c r="L47" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M47" t="n">
-        <v>7</v>
+      <c r="I47" t="n">
+        <v>3</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1</v>
-      </c>
       <c r="Y47" t="n">
         <v>1</v>
       </c>
-      <c r="Z47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
       <c r="AF47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -3577,7 +3607,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>Deriva continental y expansión del fondo oceánico</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3586,34 +3616,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="F48" t="n">
-        <v>8</v>
-      </c>
-      <c r="G48" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="E48" t="n">
+        <v>7</v>
       </c>
       <c r="J48" t="n">
         <v>7</v>
       </c>
-      <c r="K48" t="n">
-        <v>8</v>
-      </c>
       <c r="M48" t="n">
-        <v>7</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="V48" t="n">
         <v>1</v>
@@ -3621,23 +3636,20 @@
       <c r="W48" t="n">
         <v>1</v>
       </c>
-      <c r="X48" t="n">
-        <v>1</v>
-      </c>
       <c r="Y48" t="n">
         <v>1</v>
       </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
       <c r="AB48" t="n">
         <v>1</v>
       </c>
       <c r="AC48" t="n">
         <v>1</v>
       </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -3653,7 +3665,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3662,25 +3674,79 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
         <v>9</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>10.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>8.5</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="J49" t="n">
+        <v>9</v>
+      </c>
+      <c r="K49" t="n">
+        <v>9</v>
+      </c>
+      <c r="L49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>7</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
       <c r="Y49" t="n">
         <v>1</v>
       </c>
+      <c r="Z49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1</v>
+      </c>
       <c r="AF49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -3689,14 +3755,14 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3711,13 +3777,22 @@
         <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
-      </c>
-      <c r="J50" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>8</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4</v>
       </c>
       <c r="M50" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
       </c>
       <c r="V50" t="n">
         <v>1</v>
@@ -3725,6 +3800,9 @@
       <c r="W50" t="n">
         <v>1</v>
       </c>
+      <c r="X50" t="n">
+        <v>1</v>
+      </c>
       <c r="Y50" t="n">
         <v>1</v>
       </c>
@@ -3735,6 +3813,9 @@
         <v>1</v>
       </c>
       <c r="AC50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
@@ -3754,7 +3835,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3763,56 +3844,20 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="n">
         <v>9</v>
       </c>
-      <c r="F51" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I51" t="n">
-        <v>10</v>
-      </c>
       <c r="J51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>9</v>
-      </c>
-      <c r="L51" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" t="n">
         <v>9.5</v>
       </c>
-      <c r="M51" t="n">
-        <v>7</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
       <c r="V51" t="n">
         <v>1</v>
       </c>
@@ -3825,17 +3870,17 @@
       <c r="Y51" t="n">
         <v>1</v>
       </c>
-      <c r="Z51" t="n">
-        <v>1</v>
-      </c>
       <c r="AB51" t="n">
         <v>1</v>
       </c>
       <c r="AC51" t="n">
         <v>1</v>
       </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
       <c r="AF51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -3844,14 +3889,14 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>Fósiles y su formación</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3860,19 +3905,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>9</v>
       </c>
-      <c r="E52" t="n">
-        <v>4</v>
-      </c>
       <c r="F52" t="n">
         <v>8</v>
       </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>9</v>
       </c>
       <c r="M52" t="n">
         <v>7</v>
@@ -3880,22 +3928,25 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
       <c r="V52" t="n">
         <v>1</v>
       </c>
       <c r="W52" t="n">
         <v>1</v>
       </c>
-      <c r="X52" t="n">
-        <v>1</v>
-      </c>
       <c r="Y52" t="n">
         <v>1</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="Z52" t="n">
         <v>1</v>
       </c>
       <c r="AB52" t="n">
@@ -3908,7 +3959,7 @@
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -3924,7 +3975,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3933,19 +3984,40 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>9</v>
       </c>
+      <c r="F53" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6</v>
+      </c>
+      <c r="I53" t="n">
+        <v>8</v>
+      </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K53" t="n">
         <v>8</v>
       </c>
       <c r="M53" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
       </c>
       <c r="V53" t="n">
         <v>1</v>
@@ -3959,17 +4031,20 @@
       <c r="Y53" t="n">
         <v>1</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AC53" t="n">
         <v>1</v>
       </c>
+      <c r="AD53" t="n">
+        <v>1</v>
+      </c>
       <c r="AE53" t="n">
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -3985,7 +4060,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Fósiles y su formación</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3999,31 +4074,31 @@
       <c r="D54" t="n">
         <v>9</v>
       </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
       <c r="F54" t="n">
         <v>8</v>
       </c>
-      <c r="G54" t="n">
-        <v>2</v>
-      </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J54" t="n">
+        <v>7</v>
+      </c>
+      <c r="K54" t="n">
         <v>9</v>
       </c>
       <c r="M54" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
       <c r="R54" t="n">
         <v>1</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="V54" t="n">
@@ -4032,16 +4107,10 @@
       <c r="W54" t="n">
         <v>1</v>
       </c>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
       <c r="Y54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC54" t="n">
         <v>1</v>
       </c>
       <c r="AE54" t="n">
@@ -4064,7 +4133,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4073,7 +4142,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
         <v>9</v>
@@ -4081,59 +4150,47 @@
       <c r="F55" t="n">
         <v>8</v>
       </c>
-      <c r="G55" t="n">
-        <v>6</v>
-      </c>
       <c r="I55" t="n">
+        <v>7</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7</v>
+      </c>
+      <c r="K55" t="n">
+        <v>9</v>
+      </c>
+      <c r="M55" t="n">
+        <v>7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="n">
         <v>8</v>
-      </c>
-      <c r="J55" t="n">
-        <v>9</v>
-      </c>
-      <c r="K55" t="n">
-        <v>8</v>
-      </c>
-      <c r="M55" t="n">
-        <v>7</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>2</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4149,7 +4206,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Límites de placas: convergentes, divergentes y transformantes</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4158,13 +4215,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
         <v>9</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>8</v>
@@ -4175,11 +4232,8 @@
       <c r="J56" t="n">
         <v>7</v>
       </c>
-      <c r="K56" t="n">
-        <v>9</v>
-      </c>
       <c r="M56" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -4187,26 +4241,20 @@
       <c r="R56" t="n">
         <v>1</v>
       </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
       <c r="V56" t="n">
         <v>1</v>
       </c>
-      <c r="W56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1</v>
-      </c>
       <c r="Y56" t="n">
         <v>1</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AA56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC56" t="n">
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4222,7 +4270,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Mareas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4231,22 +4279,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
         <v>9</v>
       </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="I57" t="n">
-        <v>7</v>
-      </c>
-      <c r="J57" t="n">
-        <v>7</v>
-      </c>
-      <c r="K57" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
@@ -4257,18 +4302,9 @@
       <c r="R57" t="n">
         <v>1</v>
       </c>
-      <c r="S57" t="n">
-        <v>1</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
-      <c r="W57" t="n">
-        <v>1</v>
-      </c>
       <c r="AA57" t="n">
         <v>1</v>
       </c>
@@ -4279,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -4295,7 +4331,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Límites de placas: convergentes, divergentes y transformantes</t>
+          <t>Oleaje, dinámica costera y sedimentación marina</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4304,22 +4340,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
         <v>9</v>
       </c>
-      <c r="E58" t="n">
-        <v>7</v>
-      </c>
       <c r="F58" t="n">
-        <v>8</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="M58" t="n">
         <v>7</v>
@@ -4327,9 +4354,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
       <c r="V58" t="n">
         <v>1</v>
       </c>
@@ -4339,11 +4363,11 @@
       <c r="AA58" t="n">
         <v>1</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AB58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -4352,14 +4376,14 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mareas</t>
+          <t>Ondas sísmicas, magnitud e intensidad</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4368,23 +4392,20 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
         <v>9</v>
       </c>
-      <c r="E59" t="n">
-        <v>6</v>
-      </c>
       <c r="F59" t="n">
         <v>10.5</v>
       </c>
       <c r="I59" t="n">
+        <v>6</v>
+      </c>
+      <c r="M59" t="n">
         <v>9.5</v>
       </c>
-      <c r="M59" t="n">
-        <v>7</v>
-      </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
@@ -4394,17 +4415,26 @@
       <c r="V59" t="n">
         <v>1</v>
       </c>
+      <c r="W59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1</v>
+      </c>
       <c r="AA59" t="n">
         <v>1</v>
       </c>
       <c r="AB59" t="n">
         <v>1</v>
       </c>
+      <c r="AC59" t="n">
+        <v>1</v>
+      </c>
       <c r="AE59" t="n">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -4420,7 +4450,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ondas sísmicas, magnitud e intensidad</t>
+          <t>Origen del magma y vulcanismo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4429,7 +4459,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
         <v>9</v>
@@ -4440,8 +4470,11 @@
       <c r="I60" t="n">
         <v>6</v>
       </c>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
       <c r="M60" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -4487,7 +4520,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Origen del magma y vulcanismo</t>
+          <t>Planetas: tipos y comparación</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4504,12 +4537,18 @@
       <c r="F61" t="n">
         <v>10.5</v>
       </c>
+      <c r="G61" t="n">
+        <v>8.5</v>
+      </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J61" t="n">
         <v>7</v>
       </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
       <c r="M61" t="n">
         <v>7</v>
       </c>
@@ -4522,7 +4561,7 @@
       <c r="V61" t="n">
         <v>1</v>
       </c>
-      <c r="W61" t="n">
+      <c r="X61" t="n">
         <v>1</v>
       </c>
       <c r="Y61" t="n">
@@ -4537,11 +4576,8 @@
       <c r="AC61" t="n">
         <v>1</v>
       </c>
-      <c r="AE61" t="n">
-        <v>1</v>
-      </c>
       <c r="AF61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -4557,7 +4593,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Planetas: tipos y comparación</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4566,55 +4602,49 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G62" t="n">
         <v>8.5</v>
       </c>
-      <c r="I62" t="n">
-        <v>8</v>
-      </c>
-      <c r="J62" t="n">
-        <v>7</v>
-      </c>
-      <c r="K62" t="n">
-        <v>8</v>
-      </c>
       <c r="M62" t="n">
         <v>7</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="R62" t="n">
+      <c r="P62" t="n">
         <v>1</v>
       </c>
       <c r="V62" t="n">
         <v>1</v>
       </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
       <c r="X62" t="n">
         <v>1</v>
       </c>
       <c r="Y62" t="n">
         <v>1</v>
       </c>
-      <c r="AA62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB62" t="n">
+      <c r="Z62" t="n">
         <v>1</v>
       </c>
       <c r="AC62" t="n">
         <v>1</v>
       </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
       <c r="AF62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -4630,7 +4660,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4639,41 +4669,17 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
-      </c>
-      <c r="F63" t="n">
-        <v>8</v>
-      </c>
-      <c r="G63" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M63" t="n">
-        <v>7</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
-      <c r="X63" t="n">
-        <v>1</v>
-      </c>
       <c r="Y63" t="n">
         <v>1</v>
       </c>
-      <c r="Z63" t="n">
-        <v>1</v>
-      </c>
       <c r="AC63" t="n">
         <v>1</v>
       </c>
@@ -4681,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -4697,7 +4703,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
+          <t>El océano: propiedades del agua de mar y zonas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4706,25 +4712,43 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
         <v>9</v>
       </c>
-      <c r="W64" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC64" t="n">
+      <c r="F64" t="n">
+        <v>8</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10</v>
+      </c>
+      <c r="J64" t="n">
+        <v>7</v>
+      </c>
+      <c r="M64" t="n">
+        <v>7</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB64" t="n">
         <v>1</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -4740,7 +4764,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>El océano: propiedades del agua de mar y zonas</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4749,43 +4773,73 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
         <v>9</v>
       </c>
+      <c r="E65" t="n">
+        <v>9</v>
+      </c>
       <c r="F65" t="n">
         <v>8</v>
       </c>
+      <c r="G65" t="n">
+        <v>8.5</v>
+      </c>
       <c r="I65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J65" t="n">
         <v>7</v>
       </c>
+      <c r="K65" t="n">
+        <v>8</v>
+      </c>
       <c r="M65" t="n">
         <v>7</v>
       </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
       <c r="R65" t="n">
         <v>1</v>
       </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
+      <c r="W65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1</v>
+      </c>
       <c r="AA65" t="n">
         <v>1</v>
       </c>
       <c r="AB65" t="n">
         <v>1</v>
       </c>
+      <c r="AC65" t="n">
+        <v>1</v>
+      </c>
       <c r="AE65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -4801,7 +4855,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
+          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4810,50 +4864,32 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
         <v>9</v>
       </c>
-      <c r="E66" t="n">
-        <v>9</v>
-      </c>
       <c r="F66" t="n">
         <v>8</v>
       </c>
-      <c r="G66" t="n">
-        <v>8.5</v>
-      </c>
       <c r="I66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
         <v>7</v>
       </c>
-      <c r="K66" t="n">
-        <v>8</v>
-      </c>
       <c r="M66" t="n">
         <v>7</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="P66" t="n">
-        <v>1</v>
-      </c>
       <c r="R66" t="n">
         <v>1</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
       </c>
-      <c r="T66" t="n">
-        <v>1</v>
-      </c>
       <c r="V66" t="n">
         <v>1</v>
       </c>
@@ -4863,9 +4899,6 @@
       <c r="Y66" t="n">
         <v>1</v>
       </c>
-      <c r="AA66" t="n">
-        <v>1</v>
-      </c>
       <c r="AB66" t="n">
         <v>1</v>
       </c>
@@ -4876,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -4892,7 +4925,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
+          <t>Sismicidad de El Salvador</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4901,52 +4934,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
         <v>9</v>
       </c>
-      <c r="F67" t="n">
-        <v>8</v>
-      </c>
-      <c r="I67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J67" t="n">
-        <v>7</v>
-      </c>
-      <c r="M67" t="n">
-        <v>7</v>
-      </c>
-      <c r="O67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>1</v>
-      </c>
       <c r="AB67" t="n">
         <v>1</v>
       </c>
-      <c r="AC67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>1</v>
-      </c>
       <c r="AF67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -4962,7 +4959,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sismicidad de El Salvador</t>
+          <t>Sismos y fallas geológicas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4971,16 +4968,49 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
         <v>9</v>
       </c>
+      <c r="F68" t="n">
+        <v>8</v>
+      </c>
+      <c r="I68" t="n">
+        <v>5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>7</v>
+      </c>
+      <c r="M68" t="n">
+        <v>7</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>1</v>
+      </c>
       <c r="AB68" t="n">
         <v>1</v>
       </c>
+      <c r="AC68" t="n">
+        <v>1</v>
+      </c>
       <c r="AF68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
@@ -4996,7 +5026,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sismos y fallas geológicas</t>
+          <t>El sistema solar y el modelo heliocéntrico</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5005,33 +5035,42 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
         <v>9</v>
       </c>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
       <c r="F69" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" t="n">
         <v>8</v>
       </c>
-      <c r="I69" t="n">
-        <v>5</v>
-      </c>
       <c r="J69" t="n">
         <v>7</v>
       </c>
+      <c r="K69" t="n">
+        <v>8</v>
+      </c>
       <c r="M69" t="n">
         <v>7</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
       </c>
-      <c r="R69" t="n">
+      <c r="S69" t="n">
         <v>1</v>
       </c>
       <c r="V69" t="n">
         <v>1</v>
       </c>
-      <c r="W69" t="n">
+      <c r="X69" t="n">
         <v>1</v>
       </c>
       <c r="Y69" t="n">
@@ -5046,8 +5085,11 @@
       <c r="AC69" t="n">
         <v>1</v>
       </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
       <c r="AF69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -5063,7 +5105,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>El sistema solar y el modelo heliocéntrico</t>
+          <t>Sistemas terrestres y sus interacciones</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5072,61 +5114,70 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
         <v>9</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F70" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G70" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I70" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
+      <c r="K70" t="n">
+        <v>9</v>
+      </c>
+      <c r="M70" t="n">
+        <v>7</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
         <v>8</v>
-      </c>
-      <c r="J70" t="n">
-        <v>7</v>
-      </c>
-      <c r="K70" t="n">
-        <v>8</v>
-      </c>
-      <c r="M70" t="n">
-        <v>7</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>4</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -5142,7 +5193,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sistemas terrestres y sus interacciones</t>
+          <t>Suelo: formación, componentes y tipos</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5151,47 +5202,29 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>8</v>
       </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
       <c r="I71" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>7</v>
       </c>
-      <c r="K71" t="n">
-        <v>9</v>
-      </c>
-      <c r="M71" t="n">
-        <v>7</v>
-      </c>
-      <c r="N71" t="n">
-        <v>1</v>
-      </c>
       <c r="O71" t="n">
         <v>1</v>
       </c>
-      <c r="R71" t="n">
-        <v>1</v>
-      </c>
-      <c r="S71" t="n">
-        <v>1</v>
-      </c>
-      <c r="T71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" t="n">
-        <v>1</v>
-      </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
@@ -5201,20 +5234,11 @@
       <c r="Y71" t="n">
         <v>1</v>
       </c>
-      <c r="AA71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1</v>
-      </c>
       <c r="AC71" t="n">
         <v>1</v>
       </c>
-      <c r="AE71" t="n">
-        <v>1</v>
-      </c>
       <c r="AF71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
@@ -5230,7 +5254,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Suelo: formación, componentes y tipos</t>
+          <t>Tectónica de placas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5239,43 +5263,58 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
         <v>8</v>
       </c>
-      <c r="G72" t="n">
-        <v>2</v>
-      </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J72" t="n">
         <v>7</v>
       </c>
+      <c r="M72" t="n">
+        <v>7</v>
+      </c>
       <c r="O72" t="n">
         <v>1</v>
       </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
-      <c r="X72" t="n">
-        <v>1</v>
-      </c>
       <c r="Y72" t="n">
         <v>1</v>
       </c>
+      <c r="AA72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1</v>
+      </c>
       <c r="AC72" t="n">
         <v>1</v>
       </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
       <c r="AF72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -5291,7 +5330,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tectónica de placas</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5300,19 +5339,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>8</v>
       </c>
+      <c r="G73" t="n">
+        <v>2</v>
+      </c>
       <c r="I73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>7</v>
@@ -5323,35 +5365,23 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="R73" t="n">
-        <v>1</v>
-      </c>
-      <c r="S73" t="n">
-        <v>1</v>
-      </c>
       <c r="V73" t="n">
         <v>1</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
-      <c r="Y73" t="n">
-        <v>1</v>
-      </c>
       <c r="AA73" t="n">
         <v>1</v>
       </c>
       <c r="AB73" t="n">
         <v>1</v>
       </c>
-      <c r="AC73" t="n">
-        <v>1</v>
-      </c>
       <c r="AE73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -5367,7 +5397,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Tiempo geológico y datación</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5376,25 +5406,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
         <v>10</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
-      </c>
-      <c r="G74" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M74" t="n">
         <v>7</v>
@@ -5402,23 +5426,32 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
       <c r="V74" t="n">
         <v>1</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
+      <c r="Y74" t="n">
+        <v>1</v>
+      </c>
       <c r="AA74" t="n">
         <v>1</v>
       </c>
       <c r="AB74" t="n">
         <v>1</v>
       </c>
+      <c r="AC74" t="n">
+        <v>1</v>
+      </c>
       <c r="AE74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
@@ -5434,7 +5467,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tiempo geológico y datación</t>
+          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5443,20 +5476,26 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
       </c>
       <c r="I75" t="n">
         <v>6</v>
       </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
       <c r="M75" t="n">
         <v>7</v>
       </c>
@@ -5466,9 +5505,6 @@
       <c r="R75" t="n">
         <v>1</v>
       </c>
-      <c r="V75" t="n">
-        <v>1</v>
-      </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
@@ -5488,7 +5524,7 @@
         <v>1</v>
       </c>
       <c r="AF75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
@@ -5504,7 +5540,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
+          <t>Uso del suelo y su degradación</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5513,55 +5549,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
-      </c>
-      <c r="E76" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F76" t="n">
         <v>8</v>
       </c>
-      <c r="G76" t="n">
-        <v>2</v>
-      </c>
-      <c r="I76" t="n">
-        <v>6</v>
-      </c>
-      <c r="J76" t="n">
-        <v>7</v>
-      </c>
-      <c r="M76" t="n">
-        <v>7</v>
-      </c>
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
+      <c r="X76" t="n">
+        <v>1</v>
+      </c>
       <c r="Y76" t="n">
         <v>1</v>
       </c>
-      <c r="AA76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
       <c r="AE76" t="n">
         <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -5577,7 +5589,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Uso del suelo y su degradación</t>
+          <t>Volcanes: estructura, tipos y productos</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5586,31 +5598,34 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F77" t="n">
         <v>8</v>
       </c>
+      <c r="I77" t="n">
+        <v>5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7</v>
+      </c>
       <c r="O77" t="n">
         <v>1</v>
       </c>
-      <c r="W77" t="n">
-        <v>1</v>
-      </c>
-      <c r="X77" t="n">
-        <v>1</v>
-      </c>
       <c r="Y77" t="n">
         <v>1</v>
       </c>
-      <c r="AE77" t="n">
+      <c r="AB77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC77" t="n">
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -5626,43 +5641,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Volcanes: estructura, tipos y productos</t>
+          <t>Acidificación del océano</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D78" t="n">
         <v>9</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
-      </c>
-      <c r="I78" t="n">
-        <v>5</v>
-      </c>
-      <c r="J78" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Y78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>1</v>
-      </c>
       <c r="AF78" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>

--- a/internacional/Contraste_tierra_espacio.xlsx
+++ b/internacional/Contraste_tierra_espacio.xlsx
@@ -633,7 +633,7 @@
         <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -834,6 +834,9 @@
       <c r="C6" t="n">
         <v>4</v>
       </c>
+      <c r="M6" t="n">
+        <v>4.5</v>
+      </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
@@ -872,11 +875,17 @@
         <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.5</v>
+      </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
@@ -920,6 +929,9 @@
       <c r="G8" t="n">
         <v>6</v>
       </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
       <c r="I8" t="n">
         <v>10</v>
       </c>
@@ -999,9 +1011,15 @@
       <c r="G9" t="n">
         <v>6</v>
       </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
       <c r="J9" t="n">
         <v>7</v>
       </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
@@ -1058,7 +1076,7 @@
         <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
@@ -1101,13 +1119,22 @@
         <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>8.5</v>
       </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1158,6 +1185,9 @@
       <c r="E12" t="n">
         <v>6</v>
       </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
       <c r="J12" t="n">
         <v>7</v>
       </c>
@@ -1204,14 +1234,17 @@
       <c r="G13" t="n">
         <v>6</v>
       </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
       <c r="I13" t="n">
         <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
         <v>7</v>
@@ -1272,10 +1305,10 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
         <v>7</v>
@@ -1405,17 +1438,20 @@
       <c r="D16" t="n">
         <v>9</v>
       </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
         <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -1594,6 +1630,9 @@
       <c r="G19" t="n">
         <v>6</v>
       </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
       <c r="J19" t="n">
         <v>7</v>
       </c>
@@ -1664,6 +1703,9 @@
       <c r="F20" t="n">
         <v>10.5</v>
       </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
       <c r="I20" t="n">
         <v>9.5</v>
       </c>
@@ -1674,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1729,16 +1771,25 @@
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7</v>
       </c>
       <c r="I21" t="n">
         <v>8</v>
       </c>
+      <c r="J21" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1798,17 +1849,26 @@
       <c r="E22" t="n">
         <v>5</v>
       </c>
+      <c r="F22" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
       <c r="I22" t="n">
         <v>8</v>
       </c>
+      <c r="J22" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
@@ -1853,8 +1913,11 @@
       <c r="G23" t="n">
         <v>3</v>
       </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
         <v>7</v>
@@ -1900,7 +1963,7 @@
         <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
         <v>9.5</v>
@@ -1908,6 +1971,12 @@
       <c r="J24" t="n">
         <v>7</v>
       </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
@@ -1963,9 +2032,18 @@
       <c r="G25" t="n">
         <v>6</v>
       </c>
+      <c r="H25" t="n">
+        <v>7</v>
+      </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.5</v>
+      </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
@@ -2013,19 +2091,22 @@
         <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -2076,17 +2157,26 @@
       <c r="E27" t="n">
         <v>2</v>
       </c>
+      <c r="F27" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G27" t="n">
         <v>2</v>
       </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
       <c r="I27" t="n">
         <v>7</v>
       </c>
+      <c r="J27" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K27" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
@@ -2126,14 +2216,23 @@
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>8.5</v>
       </c>
+      <c r="H28" t="n">
+        <v>7</v>
+      </c>
       <c r="J28" t="n">
         <v>7</v>
       </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.5</v>
+      </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
@@ -2184,19 +2283,28 @@
         <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
       </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
       <c r="I29" t="n">
         <v>9.5</v>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5</v>
       </c>
       <c r="M29" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -2250,14 +2358,20 @@
       <c r="C30" t="n">
         <v>3</v>
       </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
       <c r="I30" t="n">
         <v>6</v>
       </c>
+      <c r="J30" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -2323,17 +2437,20 @@
       <c r="G31" t="n">
         <v>3</v>
       </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -2384,11 +2501,14 @@
       <c r="G32" t="n">
         <v>8.5</v>
       </c>
+      <c r="H32" t="n">
+        <v>5</v>
+      </c>
       <c r="J32" t="n">
         <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M32" t="n">
         <v>9.5</v>
@@ -2446,7 +2566,10 @@
         <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>2.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
       </c>
       <c r="I33" t="n">
         <v>7</v>
@@ -2455,7 +2578,7 @@
         <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M33" t="n">
         <v>7</v>
@@ -2521,14 +2644,20 @@
       <c r="G34" t="n">
         <v>3</v>
       </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
       <c r="I34" t="n">
         <v>8</v>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="V34" t="n">
         <v>1</v>
@@ -2574,19 +2703,25 @@
         <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5</v>
       </c>
       <c r="I35" t="n">
         <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.5</v>
       </c>
       <c r="M35" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -2655,6 +2790,9 @@
       <c r="F36" t="n">
         <v>10.5</v>
       </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
       <c r="I36" t="n">
         <v>10</v>
       </c>
@@ -2746,17 +2884,20 @@
       <c r="G37" t="n">
         <v>6</v>
       </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
       <c r="I37" t="n">
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M37" t="n">
         <v>7</v>
@@ -2831,8 +2972,11 @@
       <c r="G38" t="n">
         <v>8.5</v>
       </c>
+      <c r="H38" t="n">
+        <v>7</v>
+      </c>
       <c r="K38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
         <v>7</v>
@@ -2884,22 +3028,25 @@
         <v>9</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G39" t="n">
         <v>6</v>
       </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
       <c r="I39" t="n">
         <v>7</v>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L39" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -3056,20 +3203,23 @@
       <c r="G41" t="n">
         <v>6</v>
       </c>
+      <c r="H41" t="n">
+        <v>3</v>
+      </c>
       <c r="I41" t="n">
         <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M41" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="N41" t="n">
         <v>1</v>
@@ -3148,25 +3298,28 @@
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
       </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
       <c r="I42" t="n">
         <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -3236,25 +3389,28 @@
         <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
         <v>6</v>
       </c>
+      <c r="H43" t="n">
+        <v>5</v>
+      </c>
       <c r="I43" t="n">
         <v>5</v>
       </c>
       <c r="J43" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3338,8 +3494,11 @@
       <c r="G44" t="n">
         <v>6</v>
       </c>
+      <c r="H44" t="n">
+        <v>3</v>
+      </c>
       <c r="K44" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>9.5</v>
@@ -3423,17 +3582,23 @@
       <c r="G45" t="n">
         <v>6</v>
       </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
       <c r="I45" t="n">
         <v>10</v>
       </c>
+      <c r="J45" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
         <v>9.5</v>
       </c>
       <c r="M45" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3503,22 +3668,25 @@
         <v>10</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
         <v>6</v>
       </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
       <c r="I46" t="n">
         <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -3579,11 +3747,23 @@
         <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>2.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>7</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
+      <c r="J47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.5</v>
+      </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
@@ -3688,6 +3868,9 @@
       <c r="G49" t="n">
         <v>8.5</v>
       </c>
+      <c r="H49" t="n">
+        <v>7</v>
+      </c>
       <c r="I49" t="n">
         <v>10</v>
       </c>
@@ -3695,10 +3878,10 @@
         <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L49" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M49" t="n">
         <v>7</v>
@@ -3782,11 +3965,20 @@
       <c r="F50" t="n">
         <v>8</v>
       </c>
+      <c r="H50" t="n">
+        <v>4</v>
+      </c>
       <c r="I50" t="n">
         <v>4</v>
       </c>
+      <c r="J50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2</v>
+      </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
@@ -3849,11 +4041,14 @@
       <c r="D51" t="n">
         <v>9</v>
       </c>
+      <c r="H51" t="n">
+        <v>3</v>
+      </c>
       <c r="J51" t="n">
         <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
         <v>9.5</v>
@@ -3916,14 +4111,20 @@
       <c r="G52" t="n">
         <v>2</v>
       </c>
+      <c r="H52" t="n">
+        <v>4</v>
+      </c>
       <c r="I52" t="n">
         <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>4.5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -3990,22 +4191,28 @@
         <v>9</v>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
         <v>6</v>
       </c>
+      <c r="H53" t="n">
+        <v>3</v>
+      </c>
       <c r="I53" t="n">
         <v>8</v>
       </c>
       <c r="J53" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="K53" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4.5</v>
       </c>
       <c r="M53" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -4060,7 +4267,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Geología y geomorfología de El Salvador</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4069,55 +4276,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
         <v>9</v>
       </c>
-      <c r="E54" t="n">
-        <v>3</v>
-      </c>
       <c r="F54" t="n">
-        <v>8</v>
-      </c>
-      <c r="I54" t="n">
-        <v>10</v>
-      </c>
-      <c r="J54" t="n">
-        <v>7</v>
-      </c>
-      <c r="K54" t="n">
-        <v>9</v>
-      </c>
-      <c r="M54" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AF54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -4133,7 +4301,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4142,25 +4310,31 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
         <v>9</v>
       </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K55" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -4168,9 +4342,6 @@
       <c r="R55" t="n">
         <v>1</v>
       </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
@@ -4180,17 +4351,17 @@
       <c r="W55" t="n">
         <v>1</v>
       </c>
-      <c r="AA55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB55" t="n">
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
         <v>1</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4206,7 +4377,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Límites de placas: convergentes, divergentes y transformantes</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4215,25 +4386,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
         <v>9</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="I56" t="n">
         <v>7</v>
-      </c>
-      <c r="F56" t="n">
-        <v>8</v>
-      </c>
-      <c r="I56" t="n">
-        <v>10</v>
       </c>
       <c r="J56" t="n">
         <v>7</v>
       </c>
+      <c r="K56" t="n">
+        <v>7</v>
+      </c>
       <c r="M56" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -4241,20 +4412,29 @@
       <c r="R56" t="n">
         <v>1</v>
       </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
       <c r="V56" t="n">
         <v>1</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="AA56" t="n">
         <v>1</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE56" t="n">
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4270,7 +4450,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mareas</t>
+          <t>Límites de placas: convergentes, divergentes y transformantes</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4279,19 +4459,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
         <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="I57" t="n">
-        <v>9.5</v>
+        <v>10</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
@@ -4305,17 +4488,17 @@
       <c r="V57" t="n">
         <v>1</v>
       </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
       <c r="AA57" t="n">
         <v>1</v>
       </c>
-      <c r="AB57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE57" t="n">
+      <c r="AC57" t="n">
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -4331,7 +4514,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Oleaje, dinámica costera y sedimentación marina</t>
+          <t>Mareas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4345,29 +4528,44 @@
       <c r="D58" t="n">
         <v>9</v>
       </c>
+      <c r="E58" t="n">
+        <v>6</v>
+      </c>
       <c r="F58" t="n">
         <v>10.5</v>
       </c>
+      <c r="H58" t="n">
+        <v>5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.5</v>
+      </c>
       <c r="M58" t="n">
         <v>7</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
       <c r="V58" t="n">
         <v>1</v>
       </c>
-      <c r="Y58" t="n">
-        <v>1</v>
-      </c>
       <c r="AA58" t="n">
         <v>1</v>
       </c>
       <c r="AB58" t="n">
         <v>1</v>
       </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
       <c r="AF58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -4376,7 +4574,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
@@ -4467,6 +4665,9 @@
       <c r="F60" t="n">
         <v>10.5</v>
       </c>
+      <c r="H60" t="n">
+        <v>5</v>
+      </c>
       <c r="I60" t="n">
         <v>6</v>
       </c>
@@ -4540,17 +4741,20 @@
       <c r="G61" t="n">
         <v>8.5</v>
       </c>
+      <c r="H61" t="n">
+        <v>4</v>
+      </c>
       <c r="I61" t="n">
         <v>8</v>
       </c>
       <c r="J61" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M61" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O61" t="n">
         <v>1</v>
@@ -4608,11 +4812,20 @@
         <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
         <v>8.5</v>
       </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" t="n">
+        <v>5</v>
+      </c>
       <c r="M62" t="n">
         <v>7</v>
       </c>
@@ -4718,13 +4931,16 @@
         <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>7</v>
       </c>
       <c r="I64" t="n">
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="M64" t="n">
         <v>7</v>
@@ -4787,17 +5003,20 @@
       <c r="G65" t="n">
         <v>8.5</v>
       </c>
+      <c r="H65" t="n">
+        <v>4</v>
+      </c>
       <c r="I65" t="n">
         <v>7</v>
       </c>
       <c r="J65" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K65" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
@@ -4872,14 +5091,17 @@
       <c r="F66" t="n">
         <v>8</v>
       </c>
+      <c r="H66" t="n">
+        <v>5</v>
+      </c>
       <c r="I66" t="n">
         <v>6</v>
       </c>
       <c r="J66" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="M66" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O66" t="n">
         <v>1</v>
@@ -4976,14 +5198,17 @@
       <c r="F68" t="n">
         <v>8</v>
       </c>
+      <c r="H68" t="n">
+        <v>5</v>
+      </c>
       <c r="I68" t="n">
         <v>5</v>
       </c>
       <c r="J68" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="M68" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -5044,22 +5269,25 @@
         <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
         <v>3</v>
       </c>
+      <c r="H69" t="n">
+        <v>2</v>
+      </c>
       <c r="I69" t="n">
         <v>8</v>
       </c>
       <c r="J69" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M69" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
@@ -5125,17 +5353,20 @@
       <c r="F70" t="n">
         <v>8</v>
       </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
       <c r="I70" t="n">
         <v>9.5</v>
       </c>
       <c r="J70" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
@@ -5211,17 +5442,26 @@
         <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
         <v>2</v>
       </c>
+      <c r="H71" t="n">
+        <v>3</v>
+      </c>
       <c r="I71" t="n">
         <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>7</v>
       </c>
+      <c r="K71" t="n">
+        <v>2</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O71" t="n">
         <v>1</v>
       </c>
@@ -5274,6 +5514,9 @@
       <c r="F72" t="n">
         <v>8</v>
       </c>
+      <c r="H72" t="n">
+        <v>4</v>
+      </c>
       <c r="I72" t="n">
         <v>6</v>
       </c>
@@ -5281,7 +5524,7 @@
         <v>7</v>
       </c>
       <c r="M72" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -5348,19 +5591,25 @@
         <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G73" t="n">
         <v>2</v>
       </c>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
       <c r="I73" t="n">
         <v>3</v>
       </c>
       <c r="J73" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5417,9 +5666,15 @@
       <c r="F74" t="n">
         <v>10.5</v>
       </c>
+      <c r="H74" t="n">
+        <v>4</v>
+      </c>
       <c r="I74" t="n">
         <v>6</v>
       </c>
+      <c r="K74" t="n">
+        <v>3</v>
+      </c>
       <c r="M74" t="n">
         <v>7</v>
       </c>
@@ -5490,14 +5745,20 @@
       <c r="G75" t="n">
         <v>2</v>
       </c>
+      <c r="H75" t="n">
+        <v>3</v>
+      </c>
       <c r="I75" t="n">
         <v>6</v>
       </c>
       <c r="J75" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -5555,7 +5816,13 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
+      <c r="M76" t="n">
+        <v>4.5</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
@@ -5610,7 +5877,7 @@
         <v>5</v>
       </c>
       <c r="J77" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -5658,6 +5925,9 @@
       <c r="F78" t="n">
         <v>10.5</v>
       </c>
+      <c r="H78" t="n">
+        <v>7</v>
+      </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
@@ -5678,7 +5948,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Geología y geomorfología de El Salvador</t>
+          <t>Oleaje, dinámica costera y sedimentación marina</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5687,22 +5957,46 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
         <v>9</v>
       </c>
+      <c r="F79" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M79" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1</v>
+      </c>
       <c r="AF79" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>

--- a/internacional/Contraste_tierra_espacio.xlsx
+++ b/internacional/Contraste_tierra_espacio.xlsx
@@ -676,80 +676,131 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Convección del manto y energía interna de la Tierra</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
         <v>9</v>
       </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Energía geotérmica</t>
+          <t>Mareas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>9</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -758,57 +809,87 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.5</v>
       </c>
       <c r="M5" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
       <c r="AB5" t="n">
         <v>1</v>
       </c>
       <c r="AC5" t="n">
         <v>1</v>
       </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7</v>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -816,88 +897,145 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tsunamis</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1</v>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aguas subterráneas y acuíferos</t>
+          <t>Convección del manto y energía interna de la Tierra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
         <v>1</v>
       </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
       <c r="AC7" t="n">
         <v>1</v>
       </c>
-      <c r="AF7" t="n">
-        <v>3</v>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -905,145 +1043,91 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Capas internas de la Tierra</t>
+          <t>Energía geotérmica</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
       <c r="Y8" t="n">
         <v>1</v>
       </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
       <c r="AC8" t="n">
         <v>1</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>3</v>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ciclo de las rocas</t>
+          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
         <v>10.5</v>
       </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7</v>
-      </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>1</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1</v>
-      </c>
       <c r="AB9" t="n">
         <v>1</v>
       </c>
       <c r="AC9" t="n">
         <v>1</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>3</v>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -1051,60 +1135,51 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ciclones tropicales y tormentas</t>
+          <t>Tsunamis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="n">
-        <v>11</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7</v>
-      </c>
       <c r="M10" t="n">
         <v>4.5</v>
       </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
-      <c r="AF10" t="n">
-        <v>4</v>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>Aguas subterráneas y acuíferos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1121,38 +1196,26 @@
       <c r="F11" t="n">
         <v>5</v>
       </c>
-      <c r="G11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
+      <c r="I11" t="n">
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
-        <v>5</v>
-      </c>
       <c r="M11" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
       <c r="Y11" t="n">
         <v>1</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AC11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -1168,7 +1231,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Eclipses solares y lunares</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1177,31 +1240,43 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
-      </c>
-      <c r="E12" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" t="n">
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -1217,7 +1292,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>El Sol como estrella</t>
+          <t>Capas internas de la Tierra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1226,35 +1301,41 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
         <v>7</v>
       </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
       <c r="Y13" t="n">
         <v>1</v>
       </c>
@@ -1267,12 +1348,15 @@
       <c r="AC13" t="n">
         <v>1</v>
       </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -1284,7 +1368,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Ciclo de las rocas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1293,7 +1377,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
       </c>
       <c r="F14" t="n">
         <v>10.5</v>
@@ -1301,31 +1391,19 @@
       <c r="G14" t="n">
         <v>6</v>
       </c>
-      <c r="I14" t="n">
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>7</v>
-      </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="Y14" t="n">
@@ -1344,11 +1422,11 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -1360,7 +1438,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las estrellas</t>
+          <t>Ciclones tropicales y tormentas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,46 +1447,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="W15" t="n">
         <v>1</v>
       </c>
       <c r="AB15" t="n">
         <v>1</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
       <c r="AF15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -1424,7 +1481,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1433,35 +1490,47 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.5</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
       </c>
       <c r="M16" t="n">
         <v>2.5</v>
       </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
       <c r="AE16" t="n">
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -1473,7 +1542,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Formación y evolución temprana de la Tierra</t>
+          <t>Eclipses solares y lunares</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,51 +1553,33 @@
       <c r="C17" t="n">
         <v>4</v>
       </c>
-      <c r="G17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>10</v>
+      <c r="D17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB17" t="n">
         <v>1</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1</v>
-      </c>
       <c r="AF17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -1540,7 +1591,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Formación del sistema solar</t>
+          <t>El Sol como estrella</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1549,25 +1600,28 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
         <v>4</v>
       </c>
-      <c r="F18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -1575,15 +1629,12 @@
       <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
       <c r="Y18" t="n">
         <v>1</v>
       </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
       <c r="AB18" t="n">
         <v>1</v>
       </c>
@@ -1591,11 +1642,11 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -1607,7 +1658,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Galaxias y escala del universo</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1616,13 +1667,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>11</v>
-      </c>
-      <c r="E19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
         <v>10.5</v>
@@ -1630,22 +1675,25 @@
       <c r="G19" t="n">
         <v>6</v>
       </c>
-      <c r="H19" t="n">
-        <v>4</v>
+      <c r="I19" t="n">
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>7</v>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
       <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="V19" t="n">
@@ -1674,7 +1722,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -1686,7 +1734,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Ciclo de vida de las estrellas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,39 +1743,30 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
         <v>10.5</v>
       </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9.5</v>
-      </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="n">
         <v>1</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="X20" t="n">
         <v>1</v>
       </c>
       <c r="AA20" t="n">
@@ -1739,12 +1778,15 @@
       <c r="AC20" t="n">
         <v>1</v>
       </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -1756,7 +1798,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Impacto de las actividades humanas en los recursos</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1765,61 +1807,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
       </c>
-      <c r="F21" t="n">
-        <v>5</v>
-      </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>2.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
         <v>2.5</v>
       </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1</v>
-      </c>
       <c r="AE21" t="n">
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -1835,7 +1847,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>Formación y evolución temprana de la Tierra</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,36 +1856,39 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
         <v>5</v>
       </c>
-      <c r="F22" t="n">
-        <v>2.5</v>
-      </c>
       <c r="G22" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1</v>
       </c>
       <c r="AC22" t="n">
@@ -1883,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -1899,7 +1914,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Formación del sistema solar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1910,17 +1925,35 @@
       <c r="C23" t="n">
         <v>4</v>
       </c>
-      <c r="G23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
+      <c r="F23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>2.5</v>
+        <v>9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>9.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
         <v>1</v>
@@ -1932,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -1948,7 +1981,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Galaxias y escala del universo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1957,33 +1990,42 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11</v>
       </c>
       <c r="E24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
         <v>4</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>9.5</v>
       </c>
       <c r="J24" t="n">
         <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
@@ -1992,7 +2034,13 @@
       <c r="AA24" t="n">
         <v>1</v>
       </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
       <c r="AC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
@@ -2000,7 +2048,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -2012,7 +2060,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2021,46 +2069,52 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" t="n">
-        <v>6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>7</v>
+      <c r="I25" t="n">
+        <v>9.5</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M25" t="n">
         <v>4.5</v>
       </c>
-      <c r="W25" t="n">
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
         <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
       <c r="AB25" t="n">
         <v>1</v>
       </c>
       <c r="AC25" t="n">
         <v>1</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
       <c r="AF25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -2076,7 +2130,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Impacto de las actividades humanas en los recursos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2085,26 +2139,29 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K26" t="n">
         <v>2</v>
       </c>
+      <c r="L26" t="n">
+        <v>5</v>
+      </c>
       <c r="M26" t="n">
         <v>2.5</v>
       </c>
@@ -2117,14 +2174,26 @@
       <c r="V26" t="n">
         <v>1</v>
       </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
       <c r="AB26" t="n">
         <v>1</v>
       </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
       <c r="AE26" t="n">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2140,7 +2209,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2151,23 +2220,20 @@
       <c r="C27" t="n">
         <v>2</v>
       </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
         <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
         <v>4.5</v>
@@ -2178,7 +2244,13 @@
       <c r="M27" t="n">
         <v>2.5</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1</v>
       </c>
       <c r="AE27" t="n">
@@ -2189,7 +2261,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -2201,7 +2273,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2210,53 +2282,35 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="F28" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M28" t="n">
         <v>7</v>
       </c>
-      <c r="J28" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
       <c r="Y28" t="n">
         <v>1</v>
       </c>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
       <c r="AC28" t="n">
         <v>1</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -2268,7 +2322,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Recursos naturales renovables y no renovables</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2277,32 +2331,23 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
       </c>
-      <c r="G29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
       <c r="I29" t="n">
         <v>9.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="L29" t="n">
-        <v>5</v>
-      </c>
       <c r="M29" t="n">
         <v>2.5</v>
       </c>
@@ -2312,30 +2357,24 @@
       <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
       <c r="Y29" t="n">
         <v>1</v>
       </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1</v>
-      </c>
       <c r="AF29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -2347,7 +2386,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Registro fósil y cambios ambientales del pasado</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2356,16 +2395,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K30" t="n">
         <v>3</v>
@@ -2373,24 +2418,12 @@
       <c r="M30" t="n">
         <v>4.5</v>
       </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
       <c r="W30" t="n">
         <v>1</v>
       </c>
       <c r="Y30" t="n">
         <v>1</v>
       </c>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
       <c r="AB30" t="n">
         <v>1</v>
       </c>
@@ -2401,11 +2434,11 @@
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -2417,7 +2450,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2426,22 +2459,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3</v>
+      <c r="F31" t="n">
+        <v>5</v>
       </c>
       <c r="H31" t="n">
         <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>4.5</v>
@@ -2452,23 +2482,23 @@
       <c r="M31" t="n">
         <v>2.5</v>
       </c>
-      <c r="R31" t="n">
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2484,7 +2514,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2493,52 +2523,40 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7</v>
       </c>
       <c r="J32" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2554,7 +2572,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2563,52 +2581,46 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>2.5</v>
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="n">
         <v>7</v>
       </c>
       <c r="J33" t="n">
         <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
-      <c r="AA33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="n">
         <v>1</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -2624,7 +2636,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Recursos naturales renovables y no renovables</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2636,19 +2648,19 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" t="n">
         <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
         <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="J34" t="n">
         <v>4.5</v>
@@ -2656,8 +2668,17 @@
       <c r="K34" t="n">
         <v>2</v>
       </c>
+      <c r="L34" t="n">
+        <v>5</v>
+      </c>
       <c r="M34" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
       </c>
       <c r="V34" t="n">
         <v>1</v>
@@ -2665,7 +2686,13 @@
       <c r="W34" t="n">
         <v>1</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1</v>
       </c>
       <c r="AE34" t="n">
@@ -2688,48 +2715,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
+          <t>Registro fósil y cambios ambientales del pasado</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>9</v>
-      </c>
-      <c r="F35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
       </c>
-      <c r="L35" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="V35" t="n">
@@ -2754,175 +2769,118 @@
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Origen del universo: el Big Bang</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
-      </c>
-      <c r="F36" t="n">
-        <v>10.5</v>
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
       <c r="V36" t="n">
         <v>1</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
-      <c r="X36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1</v>
-      </c>
       <c r="AA36" t="n">
         <v>1</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD36" t="n">
+      <c r="AE36" t="n">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="n">
         <v>7</v>
       </c>
-      <c r="D37" t="n">
-        <v>9</v>
-      </c>
-      <c r="E37" t="n">
-        <v>9</v>
-      </c>
-      <c r="F37" t="n">
-        <v>8</v>
-      </c>
-      <c r="G37" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K37" t="n">
-        <v>6</v>
-      </c>
-      <c r="L37" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M37" t="n">
-        <v>7</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
@@ -2932,62 +2890,80 @@
       <c r="X37" t="n">
         <v>1</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="n">
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>El sistema solar y el modelo heliocéntrico</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>11</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="F38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.5</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
@@ -2996,8 +2972,20 @@
       <c r="Y38" t="n">
         <v>1</v>
       </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
       <c r="AF38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -3006,132 +2994,111 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D39" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
       </c>
       <c r="F39" t="n">
         <v>2.5</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>4.5</v>
       </c>
-      <c r="L39" t="n">
-        <v>3</v>
+      <c r="K39" t="n">
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1</v>
-      </c>
       <c r="AA39" t="n">
         <v>1</v>
       </c>
       <c r="AB39" t="n">
         <v>1</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1</v>
-      </c>
       <c r="AE39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Capas de la atmósfera y variación con la altitud</t>
+          <t>Tiempo geológico y datación</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7</v>
       </c>
       <c r="F40" t="n">
         <v>10.5</v>
       </c>
+      <c r="H40" t="n">
+        <v>4</v>
+      </c>
       <c r="I40" t="n">
-        <v>10</v>
-      </c>
-      <c r="J40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
         <v>7</v>
@@ -3142,29 +3109,29 @@
       <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
       <c r="V40" t="n">
         <v>1</v>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
       <c r="AB40" t="n">
         <v>1</v>
       </c>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
       <c r="AE40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -3173,141 +3140,108 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
         <v>7</v>
       </c>
-      <c r="D41" t="n">
-        <v>9</v>
-      </c>
-      <c r="E41" t="n">
-        <v>9</v>
-      </c>
-      <c r="F41" t="n">
-        <v>8</v>
-      </c>
-      <c r="G41" t="n">
-        <v>6</v>
-      </c>
-      <c r="H41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" t="n">
-        <v>10</v>
-      </c>
       <c r="J41" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
+        <v>7</v>
+      </c>
+      <c r="M41" t="n">
+        <v>7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="n">
         <v>4</v>
       </c>
-      <c r="L41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>7</v>
-      </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
         <v>3</v>
-      </c>
-      <c r="F42" t="n">
-        <v>5</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2</v>
       </c>
       <c r="H42" t="n">
         <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
         <v>4.5</v>
@@ -3315,47 +3249,23 @@
       <c r="K42" t="n">
         <v>2</v>
       </c>
-      <c r="L42" t="n">
-        <v>5</v>
-      </c>
       <c r="M42" t="n">
         <v>4.5</v>
       </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1</v>
-      </c>
       <c r="V42" t="n">
         <v>1</v>
       </c>
       <c r="W42" t="n">
         <v>1</v>
       </c>
-      <c r="Y42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD42" t="n">
+      <c r="AA42" t="n">
         <v>1</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3364,14 +3274,14 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3380,31 +3290,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
         <v>9</v>
       </c>
-      <c r="E43" t="n">
-        <v>8</v>
-      </c>
       <c r="F43" t="n">
         <v>5</v>
       </c>
-      <c r="G43" t="n">
-        <v>6</v>
-      </c>
       <c r="H43" t="n">
         <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
         <v>7.5</v>
@@ -3415,16 +3319,10 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
       <c r="R43" t="n">
         <v>1</v>
       </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
+      <c r="S43" t="n">
         <v>1</v>
       </c>
       <c r="V43" t="n">
@@ -3433,15 +3331,9 @@
       <c r="W43" t="n">
         <v>1</v>
       </c>
-      <c r="X43" t="n">
-        <v>1</v>
-      </c>
       <c r="Y43" t="n">
         <v>1</v>
       </c>
-      <c r="Z43" t="n">
-        <v>1</v>
-      </c>
       <c r="AA43" t="n">
         <v>1</v>
       </c>
@@ -3451,14 +3343,11 @@
       <c r="AC43" t="n">
         <v>1</v>
       </c>
-      <c r="AD43" t="n">
-        <v>1</v>
-      </c>
       <c r="AE43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3474,7 +3363,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>Origen del universo: el Big Bang</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3483,39 +3372,42 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>11</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" t="n">
         <v>7</v>
       </c>
-      <c r="D44" t="n">
-        <v>9</v>
-      </c>
-      <c r="F44" t="n">
+      <c r="K44" t="n">
         <v>8</v>
       </c>
-      <c r="G44" t="n">
-        <v>6</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>9.5</v>
       </c>
-      <c r="M44" t="n">
-        <v>7</v>
+      <c r="N44" t="n">
+        <v>1</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="P44" t="n">
-        <v>1</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
         <v>1</v>
       </c>
       <c r="V44" t="n">
@@ -3533,6 +3425,9 @@
       <c r="Z44" t="n">
         <v>1</v>
       </c>
+      <c r="AA44" t="n">
+        <v>1</v>
+      </c>
       <c r="AB44" t="n">
         <v>1</v>
       </c>
@@ -3542,11 +3437,8 @@
       <c r="AD44" t="n">
         <v>1</v>
       </c>
-      <c r="AE44" t="n">
-        <v>1</v>
-      </c>
       <c r="AF44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3562,7 +3454,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3571,19 +3463,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E45" t="n">
+        <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
         <v>6</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
         <v>10</v>
@@ -3592,13 +3487,16 @@
         <v>2.5</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M45" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3609,6 +3507,9 @@
       <c r="R45" t="n">
         <v>1</v>
       </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
@@ -3621,23 +3522,14 @@
       <c r="W45" t="n">
         <v>1</v>
       </c>
-      <c r="Y45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC45" t="n">
+      <c r="X45" t="n">
         <v>1</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3653,7 +3545,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3662,13 +3554,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G46" t="n">
         <v>6</v>
@@ -3677,21 +3569,30 @@
         <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2</v>
+        <v>4.5</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="T46" t="n">
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
         <v>1</v>
       </c>
       <c r="V46" t="n">
@@ -3700,23 +3601,29 @@
       <c r="W46" t="n">
         <v>1</v>
       </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
       <c r="Y46" t="n">
         <v>1</v>
       </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
       <c r="AB46" t="n">
         <v>1</v>
       </c>
       <c r="AC46" t="n">
         <v>1</v>
       </c>
+      <c r="AD46" t="n">
+        <v>1</v>
+      </c>
       <c r="AE46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3732,7 +3639,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Capas de la atmósfera y variación con la altitud</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3741,33 +3648,51 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
         <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" t="n">
         <v>7</v>
       </c>
-      <c r="I47" t="n">
-        <v>3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M47" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="n">
         <v>1</v>
       </c>
       <c r="AF47" t="n">
@@ -3780,14 +3705,14 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3796,40 +3721,82 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
         <v>9</v>
       </c>
       <c r="E48" t="n">
+        <v>9</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4</v>
+      </c>
+      <c r="L48" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
         <v>7</v>
-      </c>
-      <c r="J48" t="n">
-        <v>7</v>
-      </c>
-      <c r="M48" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>5</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -3845,7 +3812,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3854,40 +3821,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
         <v>5</v>
       </c>
-      <c r="L49" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M49" t="n">
-        <v>7</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -3895,9 +3859,6 @@
       <c r="P49" t="n">
         <v>1</v>
       </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
       <c r="S49" t="n">
         <v>1</v>
       </c>
@@ -3913,23 +3874,20 @@
       <c r="W49" t="n">
         <v>1</v>
       </c>
-      <c r="X49" t="n">
-        <v>1</v>
-      </c>
       <c r="Y49" t="n">
         <v>1</v>
       </c>
-      <c r="Z49" t="n">
-        <v>1</v>
-      </c>
       <c r="AB49" t="n">
         <v>1</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AD49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE49" t="n">
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -3938,14 +3896,14 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3954,38 +3912,53 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
         <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>6</v>
       </c>
       <c r="H50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K50" t="n">
         <v>2</v>
       </c>
+      <c r="L50" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M50" t="n">
         <v>2.5</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
       </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
       <c r="R50" t="n">
         <v>1</v>
       </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
       <c r="V50" t="n">
         <v>1</v>
       </c>
@@ -3998,6 +3971,9 @@
       <c r="Y50" t="n">
         <v>1</v>
       </c>
+      <c r="Z50" t="n">
+        <v>1</v>
+      </c>
       <c r="AA50" t="n">
         <v>1</v>
       </c>
@@ -4007,11 +3983,14 @@
       <c r="AC50" t="n">
         <v>1</v>
       </c>
+      <c r="AD50" t="n">
+        <v>1</v>
+      </c>
       <c r="AE50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -4027,7 +4006,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4036,47 +4015,74 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6</v>
       </c>
       <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>10</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="n">
         <v>3</v>
       </c>
-      <c r="J51" t="n">
-        <v>7</v>
-      </c>
-      <c r="K51" t="n">
-        <v>5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>4</v>
-      </c>
       <c r="AG51" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -4084,14 +4090,14 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Fósiles y su formación</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4100,42 +4106,36 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
         <v>8</v>
       </c>
-      <c r="G52" t="n">
+      <c r="J52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K52" t="n">
         <v>2</v>
       </c>
-      <c r="H52" t="n">
-        <v>4</v>
-      </c>
-      <c r="I52" t="n">
-        <v>5</v>
-      </c>
-      <c r="J52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K52" t="n">
-        <v>3</v>
-      </c>
       <c r="M52" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="P52" t="n">
-        <v>1</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>1</v>
       </c>
       <c r="V52" t="n">
@@ -4144,12 +4144,12 @@
       <c r="W52" t="n">
         <v>1</v>
       </c>
+      <c r="X52" t="n">
+        <v>1</v>
+      </c>
       <c r="Y52" t="n">
         <v>1</v>
       </c>
-      <c r="Z52" t="n">
-        <v>1</v>
-      </c>
       <c r="AB52" t="n">
         <v>1</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4191,67 +4191,31 @@
         <v>9</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
-      </c>
-      <c r="G53" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="H53" t="n">
+        <v>7</v>
+      </c>
+      <c r="I53" t="n">
         <v>3</v>
       </c>
-      <c r="I53" t="n">
-        <v>8</v>
-      </c>
       <c r="J53" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K53" t="n">
         <v>2</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>4.5</v>
       </c>
-      <c r="M53" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O53" t="n">
         <v>1</v>
       </c>
-      <c r="P53" t="n">
-        <v>1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1</v>
-      </c>
       <c r="Y53" t="n">
         <v>1</v>
       </c>
-      <c r="Z53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1</v>
-      </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4267,7 +4231,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Geología y geomorfología de El Salvador</t>
+          <t>Deriva continental y expansión del fondo oceánico</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4281,8 +4245,32 @@
       <c r="D54" t="n">
         <v>9</v>
       </c>
-      <c r="F54" t="n">
-        <v>2.5</v>
+      <c r="E54" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
+      <c r="M54" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1</v>
       </c>
       <c r="AF54" t="n">
         <v>5</v>
@@ -4301,7 +4289,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4310,41 +4298,59 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="n">
         <v>9</v>
       </c>
-      <c r="E55" t="n">
-        <v>3</v>
-      </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>10.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8.5</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I55" t="n">
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="L55" t="n">
+        <v>7.5</v>
       </c>
       <c r="M55" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
       <c r="R55" t="n">
         <v>1</v>
       </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
+      <c r="U55" t="n">
+        <v>1</v>
+      </c>
       <c r="V55" t="n">
         <v>1</v>
       </c>
@@ -4357,11 +4363,17 @@
       <c r="Y55" t="n">
         <v>1</v>
       </c>
-      <c r="AE55" t="n">
+      <c r="Z55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC55" t="n">
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4370,14 +4382,14 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4386,55 +4398,64 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
         <v>9</v>
       </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
       <c r="F56" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
         <v>5</v>
-      </c>
-      <c r="I56" t="n">
-        <v>7</v>
-      </c>
-      <c r="J56" t="n">
-        <v>7</v>
-      </c>
-      <c r="K56" t="n">
-        <v>7</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>8</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4450,7 +4471,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Límites de placas: convergentes, divergentes y transformantes</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4459,46 +4480,46 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
         <v>9</v>
       </c>
-      <c r="E57" t="n">
-        <v>7</v>
-      </c>
-      <c r="F57" t="n">
-        <v>8</v>
-      </c>
-      <c r="I57" t="n">
-        <v>10</v>
+      <c r="H57" t="n">
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>7</v>
       </c>
+      <c r="K57" t="n">
+        <v>5</v>
+      </c>
       <c r="M57" t="n">
-        <v>7</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1</v>
+      </c>
       <c r="Y57" t="n">
         <v>1</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AB57" t="n">
         <v>1</v>
       </c>
       <c r="AC57" t="n">
         <v>1</v>
       </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
       <c r="AF57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -4514,7 +4535,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mareas</t>
+          <t>Fósiles y su formación</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4523,49 +4544,67 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
         <v>9</v>
       </c>
-      <c r="E58" t="n">
-        <v>6</v>
-      </c>
       <c r="F58" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
       </c>
       <c r="H58" t="n">
+        <v>4</v>
+      </c>
+      <c r="I58" t="n">
         <v>5</v>
       </c>
-      <c r="I58" t="n">
-        <v>9.5</v>
-      </c>
       <c r="J58" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3</v>
       </c>
       <c r="M58" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
       <c r="R58" t="n">
         <v>1</v>
       </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
       <c r="V58" t="n">
         <v>1</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="W58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" t="n">
         <v>1</v>
       </c>
       <c r="AB58" t="n">
         <v>1</v>
       </c>
+      <c r="AC58" t="n">
+        <v>1</v>
+      </c>
       <c r="AE58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -4581,7 +4620,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ondas sísmicas, magnitud e intensidad</t>
+          <t>Geología y geomorfología de El Salvador</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4596,40 +4635,7 @@
         <v>9</v>
       </c>
       <c r="F59" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I59" t="n">
-        <v>6</v>
-      </c>
-      <c r="M59" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AF59" t="n">
         <v>5</v>
@@ -4648,7 +4654,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Origen del magma y vulcanismo</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4657,25 +4663,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
         <v>9</v>
       </c>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
       <c r="F60" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2</v>
       </c>
       <c r="M60" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -4683,29 +4695,26 @@
       <c r="R60" t="n">
         <v>1</v>
       </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
       <c r="V60" t="n">
         <v>1</v>
       </c>
       <c r="W60" t="n">
         <v>1</v>
       </c>
+      <c r="X60" t="n">
+        <v>1</v>
+      </c>
       <c r="Y60" t="n">
         <v>1</v>
       </c>
-      <c r="AA60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>1</v>
-      </c>
       <c r="AE60" t="n">
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -4721,7 +4730,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Planetas: tipos y comparación</t>
+          <t>Límites de placas: convergentes, divergentes y transformantes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4730,58 +4739,46 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
         <v>9</v>
       </c>
+      <c r="E61" t="n">
+        <v>7</v>
+      </c>
       <c r="F61" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K61" t="n">
+        <v>7</v>
+      </c>
+      <c r="M61" t="n">
+        <v>7</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="n">
         <v>5</v>
-      </c>
-      <c r="M61" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1</v>
-      </c>
-      <c r="X61" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>4</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -4797,7 +4794,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Ondas sísmicas, magnitud e intensidad</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4806,58 +4803,49 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F62" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>6</v>
+      </c>
+      <c r="M62" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="n">
         <v>5</v>
-      </c>
-      <c r="G62" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H62" t="n">
-        <v>2</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" t="n">
-        <v>5</v>
-      </c>
-      <c r="M62" t="n">
-        <v>7</v>
-      </c>
-      <c r="O62" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1</v>
-      </c>
-      <c r="X62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>3</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -4873,7 +4861,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
+          <t>Origen del magma y vulcanismo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4882,15 +4870,45 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
         <v>9</v>
       </c>
+      <c r="F63" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J63" t="n">
+        <v>7</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
       <c r="Y63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" t="n">
         <v>1</v>
       </c>
       <c r="AC63" t="n">
@@ -4916,7 +4934,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>El océano: propiedades del agua de mar y zonas</t>
+          <t>Planetas: tipos y comparación</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4925,25 +4943,31 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
         <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>10.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>8.5</v>
       </c>
       <c r="H64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J64" t="n">
         <v>2.5</v>
       </c>
+      <c r="K64" t="n">
+        <v>5</v>
+      </c>
       <c r="M64" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -4954,17 +4978,23 @@
       <c r="V64" t="n">
         <v>1</v>
       </c>
+      <c r="X64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1</v>
+      </c>
       <c r="AA64" t="n">
         <v>1</v>
       </c>
       <c r="AB64" t="n">
         <v>1</v>
       </c>
-      <c r="AE64" t="n">
+      <c r="AC64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -4980,7 +5010,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4989,37 +5019,28 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
-      </c>
-      <c r="E65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G65" t="n">
         <v>8.5</v>
       </c>
       <c r="H65" t="n">
-        <v>4</v>
-      </c>
-      <c r="I65" t="n">
-        <v>7</v>
-      </c>
-      <c r="J65" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="K65" t="n">
         <v>2</v>
       </c>
+      <c r="L65" t="n">
+        <v>5</v>
+      </c>
       <c r="M65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -5027,28 +5048,19 @@
       <c r="P65" t="n">
         <v>1</v>
       </c>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1</v>
-      </c>
       <c r="V65" t="n">
         <v>1</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
+      <c r="X65" t="n">
+        <v>1</v>
+      </c>
       <c r="Y65" t="n">
         <v>1</v>
       </c>
-      <c r="AA65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB65" t="n">
+      <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AC65" t="n">
@@ -5058,7 +5070,7 @@
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5074,7 +5086,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
+          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5083,55 +5095,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
         <v>9</v>
       </c>
-      <c r="F66" t="n">
-        <v>8</v>
-      </c>
-      <c r="H66" t="n">
+      <c r="W66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
         <v>5</v>
-      </c>
-      <c r="I66" t="n">
-        <v>6</v>
-      </c>
-      <c r="J66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>2</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -5147,7 +5129,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sismicidad de El Salvador</t>
+          <t>El océano: propiedades del agua de mar y zonas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5156,16 +5138,46 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
         <v>9</v>
       </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7</v>
+      </c>
+      <c r="I67" t="n">
+        <v>10</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M67" t="n">
+        <v>7</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1</v>
+      </c>
       <c r="AB67" t="n">
         <v>1</v>
       </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
       <c r="AF67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -5181,7 +5193,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sismos y fallas geológicas</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5190,32 +5202,53 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
         <v>9</v>
       </c>
+      <c r="E68" t="n">
+        <v>9</v>
+      </c>
       <c r="F68" t="n">
         <v>8</v>
       </c>
+      <c r="G68" t="n">
+        <v>8.5</v>
+      </c>
       <c r="H68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J68" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2</v>
       </c>
       <c r="M68" t="n">
         <v>2.5</v>
       </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
       <c r="R68" t="n">
         <v>1</v>
       </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
       <c r="V68" t="n">
         <v>1</v>
       </c>
@@ -5234,8 +5267,11 @@
       <c r="AC68" t="n">
         <v>1</v>
       </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
       <c r="AF68" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
@@ -5251,7 +5287,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>El sistema solar y el modelo heliocéntrico</t>
+          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5260,53 +5296,44 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
         <v>9</v>
       </c>
-      <c r="E69" t="n">
-        <v>2</v>
-      </c>
       <c r="F69" t="n">
+        <v>8</v>
+      </c>
+      <c r="H69" t="n">
         <v>5</v>
       </c>
-      <c r="G69" t="n">
-        <v>3</v>
-      </c>
-      <c r="H69" t="n">
-        <v>2</v>
-      </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J69" t="n">
         <v>2.5</v>
       </c>
-      <c r="K69" t="n">
-        <v>5</v>
-      </c>
       <c r="M69" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
       </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
       <c r="S69" t="n">
         <v>1</v>
       </c>
       <c r="V69" t="n">
         <v>1</v>
       </c>
-      <c r="X69" t="n">
+      <c r="W69" t="n">
         <v>1</v>
       </c>
       <c r="Y69" t="n">
         <v>1</v>
       </c>
-      <c r="AA69" t="n">
-        <v>1</v>
-      </c>
       <c r="AB69" t="n">
         <v>1</v>
       </c>
@@ -5317,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="AF69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -5333,7 +5360,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sistemas terrestres y sus interacciones</t>
+          <t>Sismicidad de El Salvador</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5342,73 +5369,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
         <v>9</v>
       </c>
-      <c r="E70" t="n">
-        <v>9</v>
-      </c>
-      <c r="F70" t="n">
-        <v>8</v>
-      </c>
-      <c r="H70" t="n">
-        <v>2</v>
-      </c>
-      <c r="I70" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K70" t="n">
-        <v>2</v>
-      </c>
-      <c r="M70" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N70" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>1</v>
-      </c>
       <c r="AB70" t="n">
         <v>1</v>
       </c>
-      <c r="AC70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1</v>
-      </c>
       <c r="AF70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -5424,7 +5394,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Suelo: formación, componentes y tipos</t>
+          <t>Sismos y fallas geológicas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5433,31 +5403,22 @@
         </is>
       </c>
       <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="n">
+        <v>9</v>
+      </c>
+      <c r="F71" t="n">
+        <v>8</v>
+      </c>
+      <c r="H71" t="n">
         <v>5</v>
       </c>
-      <c r="D71" t="n">
-        <v>10</v>
-      </c>
-      <c r="E71" t="n">
-        <v>2</v>
-      </c>
-      <c r="F71" t="n">
+      <c r="I71" t="n">
         <v>5</v>
       </c>
-      <c r="G71" t="n">
-        <v>2</v>
-      </c>
-      <c r="H71" t="n">
-        <v>3</v>
-      </c>
-      <c r="I71" t="n">
-        <v>3</v>
-      </c>
       <c r="J71" t="n">
-        <v>7</v>
-      </c>
-      <c r="K71" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M71" t="n">
         <v>2.5</v>
@@ -5465,20 +5426,29 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
-      <c r="X71" t="n">
-        <v>1</v>
-      </c>
       <c r="Y71" t="n">
         <v>1</v>
       </c>
+      <c r="AA71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1</v>
+      </c>
       <c r="AC71" t="n">
         <v>1</v>
       </c>
       <c r="AF71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
@@ -5494,7 +5464,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tectónica de placas</t>
+          <t>Sistemas terrestres y sus interacciones</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5503,28 +5473,34 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>8</v>
       </c>
       <c r="H72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="J72" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -5535,12 +5511,18 @@
       <c r="S72" t="n">
         <v>1</v>
       </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
       <c r="V72" t="n">
         <v>1</v>
       </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
+      <c r="X72" t="n">
+        <v>1</v>
+      </c>
       <c r="Y72" t="n">
         <v>1</v>
       </c>
@@ -5557,7 +5539,7 @@
         <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -5573,7 +5555,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Suelo: formación, componentes y tipos</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5582,7 +5564,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
         <v>10</v>
@@ -5591,19 +5573,19 @@
         <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
         <v>2</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
         <v>3</v>
       </c>
       <c r="J73" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K73" t="n">
         <v>2</v>
@@ -5614,23 +5596,20 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="V73" t="n">
-        <v>1</v>
-      </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
-      <c r="AA73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE73" t="n">
+      <c r="X73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -5646,7 +5625,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tiempo geológico y datación</t>
+          <t>Tectónica de placas</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5655,16 +5634,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E74" t="n">
         <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="H74" t="n">
         <v>4</v>
@@ -5672,16 +5651,19 @@
       <c r="I74" t="n">
         <v>6</v>
       </c>
-      <c r="K74" t="n">
-        <v>3</v>
+      <c r="J74" t="n">
+        <v>7</v>
       </c>
       <c r="M74" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
         <v>1</v>
       </c>
       <c r="V74" t="n">
@@ -5917,7 +5899,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D78" t="n">
         <v>9</v>
@@ -5936,7 +5918,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">

--- a/internacional/Contraste_tierra_espacio.xlsx
+++ b/internacional/Contraste_tierra_espacio.xlsx
@@ -816,63 +816,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>Convección del manto y energía interna de la Tierra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
         <v>9</v>
       </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>1</v>
       </c>
       <c r="AB5" t="n">
@@ -881,15 +857,6 @@
       <c r="AC5" t="n">
         <v>1</v>
       </c>
-      <c r="AD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>7</v>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -897,90 +864,33 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Energía geotérmica</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
       <c r="AC6" t="n">
         <v>1</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2</v>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -988,14 +898,14 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Convección del manto y energía interna de la Tierra</t>
+          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1004,30 +914,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K7" t="n">
         <v>9</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="M7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
         <v>1</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
@@ -1050,7 +963,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Energía geotérmica</t>
+          <t>Tsunamis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1059,20 +972,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>1</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AB8" t="n">
         <v>1</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -1084,12 +1000,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
+          <t>Aguas subterráneas y acuíferos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1099,35 +1015,29 @@
         <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>10.5</v>
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
       <c r="Y9" t="n">
         <v>1</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
       <c r="AC9" t="n">
         <v>1</v>
       </c>
+      <c r="AF9" t="n">
+        <v>3</v>
+      </c>
       <c r="AG9" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -1135,51 +1045,75 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tsunamis</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" t="n">
         <v>1</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1</v>
+      <c r="AF10" t="n">
+        <v>7</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
           <t>previo</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aguas subterráneas y acuíferos</t>
+          <t>Capas internas de la Tierra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1190,28 +1124,52 @@
       <c r="C11" t="n">
         <v>3</v>
       </c>
-      <c r="D11" t="n">
-        <v>11</v>
-      </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" t="n">
         <v>1</v>
       </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
       <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
@@ -1219,7 +1177,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -1231,7 +1189,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Ciclo de las rocas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1243,40 +1201,49 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
       </c>
       <c r="F12" t="n">
         <v>10.5</v>
       </c>
       <c r="G12" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
       <c r="Y12" t="n">
         <v>1</v>
       </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
       <c r="AF12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -1292,7 +1259,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Capas internas de la Tierra</t>
+          <t>Ciclones tropicales y tormentas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1301,34 +1268,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" t="n">
         <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="V13" t="n">
         <v>1</v>
@@ -1336,23 +1282,11 @@
       <c r="W13" t="n">
         <v>1</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1</v>
-      </c>
       <c r="AB13" t="n">
         <v>1</v>
       </c>
-      <c r="AC13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
       <c r="AF13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -1368,7 +1302,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciclo de las rocas</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1379,26 +1313,23 @@
       <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7</v>
-      </c>
       <c r="F14" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -1406,16 +1337,10 @@
       <c r="W14" t="n">
         <v>1</v>
       </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
       <c r="Y14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
@@ -1426,7 +1351,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -1438,7 +1363,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciclones tropicales y tormentas</t>
+          <t>Eclipses solares y lunares</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1449,17 +1374,23 @@
       <c r="C15" t="n">
         <v>4</v>
       </c>
-      <c r="I15" t="n">
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
         <v>7</v>
       </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
       <c r="M15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB15" t="n">
         <v>1</v>
@@ -1469,7 +1400,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -1481,7 +1412,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>El Sol como estrella</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1490,47 +1421,53 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>3</v>
-      </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -1542,7 +1479,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Eclipses solares y lunares</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1551,35 +1488,62 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G17" t="n">
         <v>6</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K17" t="n">
         <v>5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>8</v>
       </c>
       <c r="M17" t="n">
         <v>7</v>
       </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
       <c r="AB17" t="n">
         <v>1</v>
       </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -1591,7 +1555,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>El Sol como estrella</t>
+          <t>Ciclo de vida de las estrellas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1600,53 +1564,50 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" t="n">
         <v>8</v>
       </c>
-      <c r="J18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
         <v>5</v>
       </c>
-      <c r="M18" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -1658,7 +1619,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1667,13 +1628,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -1682,47 +1643,20 @@
         <v>2.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -1734,7 +1668,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las estrellas</t>
+          <t>Formación y evolución temprana de la Tierra</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,19 +1679,22 @@
       <c r="C20" t="n">
         <v>5</v>
       </c>
-      <c r="F20" t="n">
-        <v>10.5</v>
+      <c r="G20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10</v>
       </c>
       <c r="J20" t="n">
         <v>9</v>
       </c>
-      <c r="K20" t="n">
-        <v>8</v>
-      </c>
       <c r="M20" t="n">
         <v>9.5</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="n">
@@ -1766,10 +1703,10 @@
       <c r="V20" t="n">
         <v>1</v>
       </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1</v>
       </c>
       <c r="AB20" t="n">
@@ -1798,7 +1735,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Formación del sistema solar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1809,33 +1746,51 @@
       <c r="C21" t="n">
         <v>4</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="n">
         <v>9</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.5</v>
       </c>
       <c r="K21" t="n">
         <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -1847,7 +1802,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Formación y evolución temprana de la Tierra</t>
+          <t>Galaxias y escala del universo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1856,36 +1811,48 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10.5</v>
       </c>
       <c r="G22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
         <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1</v>
       </c>
       <c r="AB22" t="n">
@@ -1902,7 +1869,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -1914,7 +1881,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Formación del sistema solar</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1923,22 +1890,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
       </c>
       <c r="F23" t="n">
         <v>10.5</v>
       </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
         <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -1946,18 +1919,15 @@
       <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
       <c r="Y23" t="n">
         <v>1</v>
       </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
       <c r="AB23" t="n">
         <v>1</v>
       </c>
@@ -1965,11 +1935,11 @@
         <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -1981,7 +1951,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Galaxias y escala del universo</t>
+          <t>Impacto de las actividades humanas en los recursos</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1990,50 +1960,50 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
-      </c>
-      <c r="E24" t="n">
         <v>9</v>
       </c>
       <c r="F24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K24" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>7</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
       <c r="V24" t="n">
         <v>1</v>
       </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
         <v>1</v>
       </c>
-      <c r="AA24" t="n">
-        <v>1</v>
-      </c>
       <c r="AB24" t="n">
         <v>1</v>
       </c>
@@ -2044,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -2060,7 +2030,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2069,56 +2039,50 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
       </c>
       <c r="H25" t="n">
         <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
         <v>1</v>
       </c>
-      <c r="Y25" t="n">
-        <v>1</v>
-      </c>
       <c r="AA25" t="n">
         <v>1</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
       <c r="AC25" t="n">
         <v>1</v>
       </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
       <c r="AF25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -2130,7 +2094,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Impacto de las actividades humanas en los recursos</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2139,46 +2103,19 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
         <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>9</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>7</v>
-      </c>
-      <c r="I26" t="n">
-        <v>8</v>
       </c>
       <c r="J26" t="n">
         <v>2.5</v>
       </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>5</v>
-      </c>
       <c r="M26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y26" t="n">
         <v>1</v>
@@ -2189,15 +2126,12 @@
       <c r="AC26" t="n">
         <v>1</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -2209,7 +2143,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2218,25 +2152,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
         <v>5</v>
       </c>
-      <c r="F27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
@@ -2244,7 +2172,16 @@
       <c r="M27" t="n">
         <v>2.5</v>
       </c>
-      <c r="V27" t="n">
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1</v>
       </c>
       <c r="AA27" t="n">
@@ -2253,11 +2190,8 @@
       <c r="AC27" t="n">
         <v>1</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2273,7 +2207,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2282,19 +2216,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
       </c>
       <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" t="n">
         <v>3</v>
       </c>
-      <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.5</v>
-      </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
         <v>1</v>
@@ -2305,12 +2251,15 @@
       <c r="AC28" t="n">
         <v>1</v>
       </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
       <c r="AF28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -2322,7 +2271,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2331,19 +2280,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" t="n">
         <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
       </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
       <c r="I29" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
@@ -2354,27 +2306,24 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" t="n">
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -2386,7 +2335,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2395,50 +2344,44 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
       </c>
+      <c r="F30" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
         <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -2450,7 +2393,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2459,50 +2402,50 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
+      <c r="G31" t="n">
+        <v>8.5</v>
+      </c>
       <c r="H31" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -2514,7 +2457,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Recursos naturales renovables y no renovables</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2525,20 +2468,20 @@
       <c r="C32" t="n">
         <v>2</v>
       </c>
-      <c r="E32" t="n">
-        <v>2</v>
+      <c r="D32" t="n">
+        <v>9</v>
       </c>
       <c r="F32" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J32" t="n">
         <v>4.5</v>
@@ -2546,10 +2489,31 @@
       <c r="K32" t="n">
         <v>2</v>
       </c>
+      <c r="L32" t="n">
+        <v>5</v>
+      </c>
       <c r="M32" t="n">
         <v>2.5</v>
       </c>
-      <c r="T32" t="n">
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
         <v>1</v>
       </c>
       <c r="AE32" t="n">
@@ -2560,7 +2524,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -2572,7 +2536,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Registro fósil y cambios ambientales del pasado</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2583,36 +2547,42 @@
       <c r="C33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
         <v>4.5</v>
       </c>
-      <c r="O33" t="n">
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
       <c r="Y33" t="n">
         <v>1</v>
       </c>
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1</v>
+      </c>
       <c r="AC33" t="n">
         <v>1</v>
       </c>
@@ -2620,7 +2590,7 @@
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -2636,7 +2606,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Recursos naturales renovables y no renovables</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2647,20 +2617,17 @@
       <c r="C34" t="n">
         <v>2</v>
       </c>
-      <c r="D34" t="n">
-        <v>9</v>
-      </c>
-      <c r="F34" t="n">
-        <v>5</v>
+      <c r="E34" t="n">
+        <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>4.5</v>
@@ -2668,15 +2635,9 @@
       <c r="K34" t="n">
         <v>2</v>
       </c>
-      <c r="L34" t="n">
-        <v>5</v>
-      </c>
       <c r="M34" t="n">
         <v>2.5</v>
       </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
@@ -2686,13 +2647,7 @@
       <c r="W34" t="n">
         <v>1</v>
       </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC34" t="n">
+      <c r="AA34" t="n">
         <v>1</v>
       </c>
       <c r="AE34" t="n">
@@ -2703,7 +2658,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -2715,7 +2670,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Registro fósil y cambios ambientales del pasado</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2724,52 +2679,52 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.5</v>
       </c>
       <c r="H35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
         <v>4</v>
-      </c>
-      <c r="I35" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>3</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -2785,7 +2740,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>El sistema solar y el modelo heliocéntrico</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2794,11 +2749,17 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
       </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
       <c r="G36" t="n">
         <v>3</v>
       </c>
@@ -2806,38 +2767,50 @@
         <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
         <v>4.5</v>
       </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R36" t="n">
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
         <v>1</v>
       </c>
       <c r="V36" t="n">
         <v>1</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1</v>
       </c>
       <c r="AA36" t="n">
         <v>1</v>
       </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
       <c r="AE36" t="n">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -2849,7 +2822,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2858,25 +2831,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="G37" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -2887,23 +2866,17 @@
       <c r="W37" t="n">
         <v>1</v>
       </c>
-      <c r="X37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1</v>
-      </c>
       <c r="AA37" t="n">
         <v>1</v>
       </c>
       <c r="AB37" t="n">
         <v>1</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AE37" t="n">
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
@@ -2919,7 +2892,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>El sistema solar y el modelo heliocéntrico</t>
+          <t>Tiempo geológico y datación</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2928,64 +2901,58 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H38" t="n">
         <v>4</v>
       </c>
-      <c r="D38" t="n">
-        <v>11</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2</v>
-      </c>
-      <c r="F38" t="n">
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
         <v>5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>3</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>8</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K38" t="n">
-        <v>5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>4</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -3001,7 +2968,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3010,41 +2977,41 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
         <v>2.5</v>
       </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
       <c r="AA39" t="n">
         <v>1</v>
       </c>
@@ -3055,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3071,7 +3038,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tiempo geológico y datación</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3080,34 +3047,31 @@
         </is>
       </c>
       <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11</v>
+      </c>
+      <c r="E40" t="n">
         <v>5</v>
       </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="n">
-        <v>7</v>
-      </c>
-      <c r="F40" t="n">
-        <v>10.5</v>
+      <c r="G40" t="n">
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.5</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="V40" t="n">
         <v>1</v>
@@ -3115,23 +3079,14 @@
       <c r="W40" t="n">
         <v>1</v>
       </c>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
-      <c r="AB40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1</v>
-      </c>
       <c r="AE40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -3147,126 +3102,165 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" t="n">
         <v>4</v>
       </c>
-      <c r="F41" t="n">
+      <c r="J41" t="n">
         <v>2.5</v>
       </c>
-      <c r="H41" t="n">
+      <c r="K41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="n">
         <v>2</v>
       </c>
-      <c r="I41" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" t="n">
-        <v>7</v>
-      </c>
-      <c r="K41" t="n">
-        <v>7</v>
-      </c>
-      <c r="M41" t="n">
-        <v>7</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>4</v>
-      </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Origen del universo: el Big Bang</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
         <v>11</v>
       </c>
       <c r="E42" t="n">
+        <v>9</v>
+      </c>
+      <c r="F42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4</v>
+      </c>
+      <c r="I42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K42" t="n">
+        <v>8</v>
+      </c>
+      <c r="M42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="n">
         <v>5</v>
       </c>
-      <c r="G42" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8</v>
-      </c>
-      <c r="J42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2</v>
-      </c>
       <c r="AG42" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -3274,14 +3268,14 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Amenazas naturales geológicas e hidrometeorológicas</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3290,64 +3284,73 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
         <v>9</v>
       </c>
+      <c r="E43" t="n">
+        <v>9</v>
+      </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J43" t="n">
         <v>2.5</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
         <v>7.5</v>
       </c>
       <c r="M43" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
       <c r="R43" t="n">
         <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
-      <c r="Y43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC43" t="n">
+      <c r="X43" t="n">
         <v>1</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3356,14 +3359,14 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Origen del universo: el Big Bang</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3375,50 +3378,50 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
-      </c>
-      <c r="E44" t="n">
         <v>9</v>
       </c>
       <c r="F44" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
-        <v>7</v>
-      </c>
-      <c r="K44" t="n">
-        <v>8</v>
+        <v>4.5</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
       <c r="R44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
       <c r="Y44" t="n">
         <v>1</v>
       </c>
@@ -3435,6 +3438,9 @@
         <v>1</v>
       </c>
       <c r="AD44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
@@ -3454,7 +3460,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Capas de la atmósfera y variación con la altitud</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3463,47 +3469,29 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
         <v>9</v>
       </c>
-      <c r="E45" t="n">
-        <v>9</v>
-      </c>
       <c r="F45" t="n">
-        <v>8</v>
-      </c>
-      <c r="G45" t="n">
-        <v>6</v>
-      </c>
-      <c r="H45" t="n">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="I45" t="n">
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>6</v>
-      </c>
-      <c r="L45" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="M45" t="n">
         <v>7</v>
       </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
       <c r="R45" t="n">
         <v>1</v>
       </c>
@@ -3513,23 +3501,23 @@
       <c r="T45" t="n">
         <v>1</v>
       </c>
-      <c r="U45" t="n">
-        <v>1</v>
-      </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3545,7 +3533,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3554,32 +3542,41 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
         <v>9</v>
       </c>
+      <c r="E46" t="n">
+        <v>9</v>
+      </c>
       <c r="F46" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G46" t="n">
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M46" t="n">
         <v>4.5</v>
       </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
@@ -3592,6 +3589,9 @@
       <c r="S46" t="n">
         <v>1</v>
       </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
       <c r="U46" t="n">
         <v>1</v>
       </c>
@@ -3601,29 +3601,23 @@
       <c r="W46" t="n">
         <v>1</v>
       </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
       <c r="Y46" t="n">
         <v>1</v>
       </c>
-      <c r="Z46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1</v>
-      </c>
       <c r="AB46" t="n">
         <v>1</v>
       </c>
       <c r="AC46" t="n">
         <v>1</v>
       </c>
-      <c r="AD46" t="n">
-        <v>1</v>
-      </c>
       <c r="AE46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3639,7 +3633,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Capas de la atmósfera y variación con la altitud</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3653,25 +3647,37 @@
       <c r="D47" t="n">
         <v>9</v>
       </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
       <c r="F47" t="n">
-        <v>10.5</v>
+        <v>5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K47" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>5</v>
       </c>
       <c r="M47" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="R47" t="n">
+      <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="S47" t="n">
@@ -3680,16 +3686,22 @@
       <c r="T47" t="n">
         <v>1</v>
       </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="Y47" t="n">
         <v>1</v>
       </c>
       <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="n">
         <v>1</v>
       </c>
       <c r="AE47" t="n">
@@ -3705,14 +3717,14 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3721,40 +3733,37 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
         <v>9</v>
       </c>
       <c r="E48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
         <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
         <v>7.5</v>
       </c>
       <c r="M48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
@@ -3765,9 +3774,6 @@
       <c r="R48" t="n">
         <v>1</v>
       </c>
-      <c r="S48" t="n">
-        <v>1</v>
-      </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
@@ -3786,17 +3792,26 @@
       <c r="Y48" t="n">
         <v>1</v>
       </c>
+      <c r="Z48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
       <c r="AB48" t="n">
         <v>1</v>
       </c>
       <c r="AC48" t="n">
         <v>1</v>
       </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
       <c r="AE48" t="n">
         <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -3812,7 +3827,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3821,37 +3836,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
         <v>9</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" t="n">
         <v>3</v>
-      </c>
-      <c r="F49" t="n">
-        <v>5</v>
-      </c>
-      <c r="G49" t="n">
-        <v>2</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.5</v>
       </c>
       <c r="K49" t="n">
         <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="M49" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -3859,9 +3865,6 @@
       <c r="P49" t="n">
         <v>1</v>
       </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
@@ -3874,12 +3877,21 @@
       <c r="W49" t="n">
         <v>1</v>
       </c>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
       <c r="Y49" t="n">
         <v>1</v>
       </c>
+      <c r="Z49" t="n">
+        <v>1</v>
+      </c>
       <c r="AB49" t="n">
         <v>1</v>
       </c>
+      <c r="AC49" t="n">
+        <v>1</v>
+      </c>
       <c r="AD49" t="n">
         <v>1</v>
       </c>
@@ -3887,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -3896,14 +3908,14 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3912,37 +3924,34 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
-      </c>
-      <c r="E50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="G50" t="n">
         <v>6</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K50" t="n">
         <v>2</v>
       </c>
       <c r="L50" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M50" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
@@ -3965,15 +3974,9 @@
       <c r="W50" t="n">
         <v>1</v>
       </c>
-      <c r="X50" t="n">
-        <v>1</v>
-      </c>
       <c r="Y50" t="n">
         <v>1</v>
       </c>
-      <c r="Z50" t="n">
-        <v>1</v>
-      </c>
       <c r="AA50" t="n">
         <v>1</v>
       </c>
@@ -3983,14 +3986,11 @@
       <c r="AC50" t="n">
         <v>1</v>
       </c>
-      <c r="AD50" t="n">
-        <v>1</v>
-      </c>
       <c r="AE50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -3999,14 +3999,14 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4015,13 +4015,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>6</v>
@@ -4030,7 +4030,7 @@
         <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J51" t="n">
         <v>2.5</v>
@@ -4038,39 +4038,27 @@
       <c r="K51" t="n">
         <v>2</v>
       </c>
-      <c r="L51" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M51" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
       <c r="V51" t="n">
         <v>1</v>
       </c>
       <c r="W51" t="n">
         <v>1</v>
       </c>
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
       <c r="Y51" t="n">
         <v>1</v>
       </c>
-      <c r="AA51" t="n">
-        <v>1</v>
-      </c>
       <c r="AB51" t="n">
         <v>1</v>
       </c>
@@ -4081,7 +4069,7 @@
         <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -4090,14 +4078,14 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4109,19 +4097,16 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
-      </c>
-      <c r="G52" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I52" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>2.5</v>
@@ -4130,37 +4115,16 @@
         <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1</v>
-      </c>
       <c r="Y52" t="n">
         <v>1</v>
       </c>
-      <c r="AB52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1</v>
-      </c>
       <c r="AF52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4176,7 +4140,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Deriva continental y expansión del fondo oceánico</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4185,37 +4149,40 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
         <v>9</v>
       </c>
-      <c r="F53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H53" t="n">
+      <c r="E53" t="n">
         <v>7</v>
       </c>
-      <c r="I53" t="n">
-        <v>3</v>
-      </c>
       <c r="J53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O53" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="Y53" t="n">
         <v>1</v>
       </c>
+      <c r="AA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1</v>
+      </c>
       <c r="AF53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4231,7 +4198,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4240,41 +4207,83 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="n">
+        <v>9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>7</v>
+      </c>
+      <c r="I54" t="n">
+        <v>10</v>
+      </c>
+      <c r="J54" t="n">
+        <v>9</v>
+      </c>
+      <c r="K54" t="n">
         <v>5</v>
       </c>
-      <c r="D54" t="n">
-        <v>9</v>
-      </c>
-      <c r="E54" t="n">
+      <c r="L54" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M54" t="n">
         <v>7</v>
       </c>
-      <c r="J54" t="n">
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
         <v>7</v>
       </c>
-      <c r="M54" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>5</v>
-      </c>
       <c r="AG54" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -4282,14 +4291,14 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4298,83 +4307,65 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="H55" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="K55" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="n">
         <v>5</v>
       </c>
-      <c r="L55" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M55" t="n">
-        <v>7</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>7</v>
-      </c>
       <c r="AG55" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -4382,14 +4373,14 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4398,64 +4389,46 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
         <v>9</v>
       </c>
-      <c r="E56" t="n">
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
+      <c r="K56" t="n">
+        <v>5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
         <v>4</v>
-      </c>
-      <c r="F56" t="n">
-        <v>8</v>
-      </c>
-      <c r="H56" t="n">
-        <v>4</v>
-      </c>
-      <c r="I56" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>5</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4471,7 +4444,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>Fósiles y su formación</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4480,22 +4453,43 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
         <v>9</v>
       </c>
+      <c r="F57" t="n">
+        <v>8</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2</v>
+      </c>
       <c r="H57" t="n">
+        <v>4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K57" t="n">
         <v>3</v>
       </c>
-      <c r="J57" t="n">
-        <v>7</v>
-      </c>
-      <c r="K57" t="n">
-        <v>5</v>
-      </c>
       <c r="M57" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
       </c>
       <c r="V57" t="n">
         <v>1</v>
@@ -4503,12 +4497,12 @@
       <c r="W57" t="n">
         <v>1</v>
       </c>
-      <c r="X57" t="n">
-        <v>1</v>
-      </c>
       <c r="Y57" t="n">
         <v>1</v>
       </c>
+      <c r="Z57" t="n">
+        <v>1</v>
+      </c>
       <c r="AB57" t="n">
         <v>1</v>
       </c>
@@ -4519,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -4535,7 +4529,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fósiles y su formación</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4544,31 +4538,34 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
         <v>9</v>
       </c>
       <c r="F58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
         <v>8</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4</v>
-      </c>
-      <c r="I58" t="n">
-        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>4.5</v>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4.5</v>
       </c>
       <c r="M58" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -4588,23 +4585,26 @@
       <c r="W58" t="n">
         <v>1</v>
       </c>
+      <c r="X58" t="n">
+        <v>1</v>
+      </c>
       <c r="Y58" t="n">
         <v>1</v>
       </c>
       <c r="Z58" t="n">
         <v>1</v>
       </c>
-      <c r="AB58" t="n">
-        <v>1</v>
-      </c>
       <c r="AC58" t="n">
         <v>1</v>
       </c>
+      <c r="AD58" t="n">
+        <v>1</v>
+      </c>
       <c r="AE58" t="n">
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
